--- a/Sindhi Muslim/Staff Attendance/Staff Attendance - 2nd Year - 3rd QTR.xlsx
+++ b/Sindhi Muslim/Staff Attendance/Staff Attendance - 2nd Year - 3rd QTR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F7A876-32D4-4039-A365-6B7B32BBBCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DF5746-25C6-46FB-8336-99EBF8D28A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY-2025" sheetId="11" r:id="rId1"/>
@@ -284,7 +284,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -577,11 +577,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -655,14 +705,20 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -679,25 +735,34 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -742,41 +807,41 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="228">
+  <dxfs count="176">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -819,6 +884,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -829,6 +914,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -849,6 +944,306 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -859,6 +1254,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -869,6 +1284,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -879,6 +1314,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -919,6 +1364,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -949,6 +1404,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -989,6 +1464,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -999,6 +1484,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1039,6 +1554,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1049,6 +1584,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1059,6 +1614,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1089,6 +1654,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1099,6 +1674,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1109,6 +1694,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1119,6 +1724,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1129,6 +1744,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1139,6 +1764,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1199,6 +1834,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1209,6 +1854,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1219,6 +1904,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1229,6 +1934,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1239,6 +1954,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1259,6 +1984,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1269,6 +2004,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1279,6 +2024,356 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1289,1581 +2384,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3347,37 +2892,37 @@
   <sheetData>
     <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="36"/>
     </row>
     <row r="3" spans="1:21" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="15" t="str">
+      <c r="A3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="68" t="str">
         <f t="shared" ref="D3:O3" si="0">TEXT(D4,"ddd")</f>
         <v>Mon</v>
       </c>
@@ -3428,11 +2973,11 @@
       <c r="P3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
-      <c r="S3" s="37"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="38"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="41"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -3441,10 +2986,10 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="69">
         <v>45705</v>
       </c>
       <c r="E4" s="7">
@@ -3506,16 +3051,16 @@
       <c r="B5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="47" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -3527,7 +3072,7 @@
       <c r="I5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="40" t="s">
+      <c r="J5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -3546,15 +3091,15 @@
         <v>6</v>
       </c>
       <c r="P5" s="3">
-        <f>COUNTIF(D5:O5,"P")</f>
+        <f t="shared" ref="P5:P13" si="1">COUNTIF(D5:O5,"P")</f>
         <v>10</v>
       </c>
       <c r="Q5" s="4">
-        <f>COUNTIF(D5:O5,"A")</f>
+        <f t="shared" ref="Q5:Q13" si="2">COUNTIF(D5:O5,"A")</f>
         <v>0</v>
       </c>
       <c r="R5" s="4">
-        <f>COUNTIF(D5:O5,"L")</f>
+        <f t="shared" ref="R5:R13" si="3">COUNTIF(D5:O5,"L")</f>
         <v>0</v>
       </c>
       <c r="S5" s="4">
@@ -3575,16 +3120,16 @@
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="43"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3594,7 +3139,7 @@
       <c r="I6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="40"/>
+      <c r="J6" s="42"/>
       <c r="K6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3611,15 +3156,15 @@
         <v>6</v>
       </c>
       <c r="P6" s="3">
-        <f>COUNTIF(D6:O6,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q6" s="4">
-        <f>COUNTIF(D6:O6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R6" s="4">
-        <f>COUNTIF(D6:O6,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S6" s="4">
@@ -3629,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="U6" s="16">
-        <f t="shared" ref="U6:U13" si="1">P6+R6+S6+T6</f>
+        <f t="shared" ref="U6:U12" si="4">P6+R6+S6+T6</f>
         <v>12</v>
       </c>
     </row>
@@ -3640,16 +3185,16 @@
       <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="43"/>
+      <c r="F7" s="47"/>
       <c r="G7" s="4" t="s">
         <v>6</v>
       </c>
@@ -3659,7 +3204,7 @@
       <c r="I7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="40"/>
+      <c r="J7" s="42"/>
       <c r="K7" s="4" t="s">
         <v>6</v>
       </c>
@@ -3676,15 +3221,15 @@
         <v>6</v>
       </c>
       <c r="P7" s="3">
-        <f>COUNTIF(D7:O7,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q7" s="4">
-        <f>COUNTIF(D7:O7,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R7" s="4">
-        <f>COUNTIF(D7:O7,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S7" s="4">
@@ -3694,7 +3239,7 @@
         <v>1</v>
       </c>
       <c r="U7" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
     </row>
@@ -3705,16 +3250,16 @@
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="43"/>
+      <c r="F8" s="47"/>
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
@@ -3724,7 +3269,7 @@
       <c r="I8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="40"/>
+      <c r="J8" s="42"/>
       <c r="K8" s="4" t="s">
         <v>6</v>
       </c>
@@ -3741,15 +3286,15 @@
         <v>6</v>
       </c>
       <c r="P8" s="3">
-        <f>COUNTIF(D8:O8,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q8" s="4">
-        <f>COUNTIF(D8:O8,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R8" s="4">
-        <f>COUNTIF(D8:O8,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S8" s="4">
@@ -3759,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="U8" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
     </row>
@@ -3770,16 +3315,16 @@
       <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="43"/>
+      <c r="F9" s="47"/>
       <c r="G9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3789,7 +3334,7 @@
       <c r="I9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="40"/>
+      <c r="J9" s="42"/>
       <c r="K9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3806,15 +3351,15 @@
         <v>6</v>
       </c>
       <c r="P9" s="3">
-        <f>COUNTIF(D9:O9,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q9" s="4">
-        <f>COUNTIF(D9:O9,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R9" s="4">
-        <f>COUNTIF(D9:O9,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S9" s="4">
@@ -3824,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="U9" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
     </row>
@@ -3835,16 +3380,16 @@
       <c r="B10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="43"/>
+      <c r="F10" s="47"/>
       <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3854,7 +3399,7 @@
       <c r="I10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="40"/>
+      <c r="J10" s="42"/>
       <c r="K10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3871,15 +3416,15 @@
         <v>6</v>
       </c>
       <c r="P10" s="3">
-        <f>COUNTIF(D10:O10,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q10" s="4">
-        <f>COUNTIF(D10:O10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R10" s="4">
-        <f>COUNTIF(D10:O10,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S10" s="4">
@@ -3889,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="U10" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
     </row>
@@ -3900,16 +3445,16 @@
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="43"/>
+      <c r="F11" s="47"/>
       <c r="G11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3919,7 +3464,7 @@
       <c r="I11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="40"/>
+      <c r="J11" s="42"/>
       <c r="K11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3936,15 +3481,15 @@
         <v>6</v>
       </c>
       <c r="P11" s="3">
-        <f>COUNTIF(D11:O11,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q11" s="4">
-        <f>COUNTIF(D11:O11,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R11" s="4">
-        <f>COUNTIF(D11:O11,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S11" s="4">
@@ -3954,27 +3499,27 @@
         <v>1</v>
       </c>
       <c r="U11" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="42"/>
+      <c r="F12" s="48"/>
       <c r="G12" s="4" t="s">
         <v>6</v>
       </c>
@@ -3984,7 +3529,7 @@
       <c r="I12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="29"/>
+      <c r="J12" s="43"/>
       <c r="K12" s="4" t="s">
         <v>6</v>
       </c>
@@ -4001,15 +3546,15 @@
         <v>6</v>
       </c>
       <c r="P12" s="3">
-        <f>COUNTIF(D12:O12,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q12" s="4">
-        <f>COUNTIF(D12:O12,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R12" s="4">
-        <f>COUNTIF(D12:O12,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S12" s="4">
@@ -4019,7 +3564,7 @@
         <v>1</v>
       </c>
       <c r="U12" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
     </row>
@@ -4030,16 +3575,16 @@
       <c r="B13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="72" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="44"/>
+      <c r="F13" s="49"/>
       <c r="G13" s="6" t="s">
         <v>24</v>
       </c>
@@ -4049,7 +3594,7 @@
       <c r="I13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="41"/>
+      <c r="J13" s="44"/>
       <c r="K13" s="6" t="s">
         <v>6</v>
       </c>
@@ -4066,15 +3611,15 @@
         <v>6</v>
       </c>
       <c r="P13" s="5">
-        <f>COUNTIF(D13:O13,"P")</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="Q13" s="6">
-        <f>COUNTIF(D13:O13,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R13" s="6">
-        <f>COUNTIF(D13:O13,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S13" s="6">
@@ -4089,92 +3634,92 @@
     </row>
     <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="34"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="36"/>
     </row>
     <row r="16" spans="1:21" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="15" t="str">
-        <f t="shared" ref="D16:O16" si="2">TEXT(D17,"ddd")</f>
+      <c r="A16" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="68" t="str">
+        <f t="shared" ref="D16:O16" si="5">TEXT(D17,"ddd")</f>
         <v>Mon</v>
       </c>
       <c r="E16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
       <c r="F16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
       <c r="G16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
       <c r="H16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
       <c r="I16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
       <c r="J16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
       <c r="K16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
       <c r="L16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
       <c r="M16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
       <c r="N16" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
       <c r="O16" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
       <c r="P16" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="38"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="41"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -4183,10 +3728,10 @@
       <c r="B17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="69">
         <v>45705</v>
       </c>
       <c r="E17" s="7">
@@ -4249,16 +3794,16 @@
       <c r="B18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F18" s="47" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="4" t="s">
@@ -4270,7 +3815,7 @@
       <c r="I18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J18" s="29" t="s">
+      <c r="J18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="K18" s="4" t="s">
@@ -4289,15 +3834,15 @@
         <v>6</v>
       </c>
       <c r="P18" s="24">
-        <f>COUNTIF(D18:O18,"P")</f>
+        <f t="shared" ref="P18:P25" si="6">COUNTIF(D18:O18,"P")</f>
         <v>10</v>
       </c>
       <c r="Q18" s="8">
-        <f>COUNTIF(D18:O18,"A")</f>
+        <f t="shared" ref="Q18:Q25" si="7">COUNTIF(D18:O18,"A")</f>
         <v>0</v>
       </c>
       <c r="R18" s="8">
-        <f>COUNTIF(D18:O18,"L")</f>
+        <f t="shared" ref="R18:R25" si="8">COUNTIF(D18:O18,"L")</f>
         <v>0</v>
       </c>
       <c r="S18" s="4">
@@ -4319,16 +3864,16 @@
       <c r="B19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="43"/>
+      <c r="F19" s="47"/>
       <c r="G19" s="4" t="s">
         <v>6</v>
       </c>
@@ -4338,7 +3883,7 @@
       <c r="I19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="30"/>
+      <c r="J19" s="45"/>
       <c r="K19" s="4" t="s">
         <v>6</v>
       </c>
@@ -4355,15 +3900,15 @@
         <v>6</v>
       </c>
       <c r="P19" s="24">
-        <f>COUNTIF(D19:O19,"P")</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="Q19" s="8">
-        <f>COUNTIF(D19:O19,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R19" s="8">
-        <f>COUNTIF(D19:O19,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S19" s="4">
@@ -4373,28 +3918,28 @@
         <v>1</v>
       </c>
       <c r="U19" s="16">
-        <f t="shared" ref="U19:U25" si="3">P19+R19+S19+T19</f>
+        <f t="shared" ref="U19:U25" si="9">P19+R19+S19+T19</f>
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <f t="shared" ref="A20:A25" si="4">IF(B20="","",A19+1)</f>
+        <f t="shared" ref="A20:A25" si="10">IF(B20="","",A19+1)</f>
         <v>3</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="43"/>
+      <c r="F20" s="47"/>
       <c r="G20" s="4" t="s">
         <v>6</v>
       </c>
@@ -4404,7 +3949,7 @@
       <c r="I20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="30"/>
+      <c r="J20" s="45"/>
       <c r="K20" s="4" t="s">
         <v>6</v>
       </c>
@@ -4421,15 +3966,15 @@
         <v>6</v>
       </c>
       <c r="P20" s="24">
-        <f>COUNTIF(D20:O20,"P")</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="Q20" s="8">
-        <f>COUNTIF(D20:O20,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R20" s="8">
-        <f>COUNTIF(D20:O20,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S20" s="4">
@@ -4439,28 +3984,28 @@
         <v>1</v>
       </c>
       <c r="U20" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="43"/>
+      <c r="F21" s="47"/>
       <c r="G21" s="4" t="s">
         <v>6</v>
       </c>
@@ -4470,7 +4015,7 @@
       <c r="I21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J21" s="30"/>
+      <c r="J21" s="45"/>
       <c r="K21" s="4" t="s">
         <v>6</v>
       </c>
@@ -4487,15 +4032,15 @@
         <v>6</v>
       </c>
       <c r="P21" s="24">
-        <f>COUNTIF(D21:O21,"P")</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="Q21" s="8">
-        <f>COUNTIF(D21:O21,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <f>COUNTIF(D21:O21,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S21" s="4">
@@ -4505,28 +4050,28 @@
         <v>1</v>
       </c>
       <c r="U21" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="43"/>
+      <c r="F22" s="47"/>
       <c r="G22" s="4" t="s">
         <v>6</v>
       </c>
@@ -4536,7 +4081,7 @@
       <c r="I22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J22" s="30"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="4" t="s">
         <v>6</v>
       </c>
@@ -4553,15 +4098,15 @@
         <v>6</v>
       </c>
       <c r="P22" s="24">
-        <f>COUNTIF(D22:O22,"P")</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="Q22" s="8">
-        <f>COUNTIF(D22:O22,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R22" s="8">
-        <f>COUNTIF(D22:O22,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S22" s="4">
@@ -4571,28 +4116,28 @@
         <v>1</v>
       </c>
       <c r="U22" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="43"/>
+      <c r="F23" s="47"/>
       <c r="G23" s="4" t="s">
         <v>6</v>
       </c>
@@ -4602,7 +4147,7 @@
       <c r="I23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J23" s="30"/>
+      <c r="J23" s="45"/>
       <c r="K23" s="4" t="s">
         <v>6</v>
       </c>
@@ -4619,15 +4164,15 @@
         <v>6</v>
       </c>
       <c r="P23" s="24">
-        <f>COUNTIF(D23:O23,"P")</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Q23" s="8">
-        <f>COUNTIF(D23:O23,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R23" s="8">
-        <f>COUNTIF(D23:O23,"L")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S23" s="4">
@@ -4637,28 +4182,28 @@
         <v>1</v>
       </c>
       <c r="U23" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="71" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="43"/>
+      <c r="F24" s="47"/>
       <c r="G24" s="11" t="s">
         <v>6</v>
       </c>
@@ -4668,7 +4213,7 @@
       <c r="I24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J24" s="30"/>
+      <c r="J24" s="45"/>
       <c r="K24" s="11" t="s">
         <v>6</v>
       </c>
@@ -4685,15 +4230,15 @@
         <v>6</v>
       </c>
       <c r="P24" s="25">
-        <f>COUNTIF(D24:O24,"P")</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Q24" s="12">
-        <f>COUNTIF(D24:O24,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R24" s="8">
-        <f>COUNTIF(D24:O24,"L")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S24" s="11">
@@ -4703,28 +4248,28 @@
         <v>1</v>
       </c>
       <c r="U24" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <f t="shared" si="4"/>
+      <c r="A25" s="5">
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="72" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="44"/>
+      <c r="F25" s="49"/>
       <c r="G25" s="6" t="s">
         <v>6</v>
       </c>
@@ -4734,7 +4279,7 @@
       <c r="I25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J25" s="31"/>
+      <c r="J25" s="46"/>
       <c r="K25" s="6" t="s">
         <v>6</v>
       </c>
@@ -4751,15 +4296,15 @@
         <v>6</v>
       </c>
       <c r="P25" s="26">
-        <f>COUNTIF(D25:O25,"P")</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="Q25" s="9">
-        <f>COUNTIF(D25:O25,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R25" s="9">
-        <f>COUNTIF(D25:O25,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S25" s="6">
@@ -4769,12 +4314,15 @@
         <v>1</v>
       </c>
       <c r="U25" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="P3:U3"/>
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="P16:U16"/>
@@ -4782,75 +4330,72 @@
     <mergeCell ref="J18:J25"/>
     <mergeCell ref="F5:F13"/>
     <mergeCell ref="F18:F25"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="P3:U3"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5 J5 D3:O4 D16:O17 D5:E13 G5:I13 K5:O13">
-    <cfRule type="expression" dxfId="227" priority="217">
+  <conditionalFormatting sqref="D18:E25">
+    <cfRule type="expression" dxfId="175" priority="28">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="29" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="173" priority="30" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:O4 F5 J5 D5:E13 G5:I13 K5:O13 D16:O17">
+    <cfRule type="expression" dxfId="172" priority="217">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5 J5 D5:E13 G5:I13 K5:O13">
-    <cfRule type="cellIs" dxfId="226" priority="218" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="218" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="225" priority="219" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:E25">
-    <cfRule type="expression" dxfId="224" priority="28">
-      <formula>D$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="223" priority="29" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="219" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="expression" dxfId="221" priority="4">
+    <cfRule type="expression" dxfId="169" priority="4">
       <formula>F$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="5" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="219" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="6" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18:I25">
-    <cfRule type="expression" dxfId="218" priority="22">
+    <cfRule type="expression" dxfId="166" priority="22">
       <formula>G$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="217" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="23" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="24" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J18">
-    <cfRule type="expression" dxfId="215" priority="7">
+    <cfRule type="expression" dxfId="163" priority="7">
       <formula>J$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="8" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="9" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:O25">
-    <cfRule type="expression" dxfId="212" priority="10">
+    <cfRule type="expression" dxfId="160" priority="10">
       <formula>K$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="11" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="12" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4879,55 +4424,55 @@
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
-      <c r="AK2" s="33"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="33"/>
-      <c r="AN2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="36"/>
     </row>
     <row r="3" spans="1:40" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
+      <c r="A3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="15" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Sat</v>
@@ -5055,11 +4600,11 @@
       <c r="AI3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="37"/>
-      <c r="AK3" s="37"/>
-      <c r="AL3" s="37"/>
-      <c r="AM3" s="37"/>
-      <c r="AN3" s="38"/>
+      <c r="AJ3" s="40"/>
+      <c r="AK3" s="40"/>
+      <c r="AL3" s="40"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="41"/>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -5196,7 +4741,7 @@
       <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -5217,7 +4762,7 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="40" t="s">
+      <c r="L5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="M5" s="4" t="s">
@@ -5238,7 +4783,7 @@
       <c r="R5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="S5" s="40" t="s">
+      <c r="S5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="T5" s="4" t="s">
@@ -5259,7 +4804,7 @@
       <c r="Y5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="40" t="s">
+      <c r="Z5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="AA5" s="4" t="s">
@@ -5274,16 +4819,16 @@
       <c r="AD5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE5" s="45" t="s">
+      <c r="AE5" s="50" t="s">
         <v>43</v>
       </c>
       <c r="AF5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG5" s="40" t="s">
+      <c r="AG5" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="AH5" s="53" t="s">
+      <c r="AH5" s="58" t="s">
         <v>44</v>
       </c>
       <c r="AI5" s="3">
@@ -5322,7 +4867,7 @@
       <c r="D6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="40"/>
+      <c r="E6" s="42"/>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
@@ -5341,7 +4886,7 @@
       <c r="K6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="40"/>
+      <c r="L6" s="42"/>
       <c r="M6" s="4" t="s">
         <v>6</v>
       </c>
@@ -5360,7 +4905,7 @@
       <c r="R6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S6" s="40"/>
+      <c r="S6" s="42"/>
       <c r="T6" s="4" t="s">
         <v>6</v>
       </c>
@@ -5379,7 +4924,7 @@
       <c r="Y6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z6" s="40"/>
+      <c r="Z6" s="42"/>
       <c r="AA6" s="4" t="s">
         <v>6</v>
       </c>
@@ -5392,12 +4937,12 @@
       <c r="AD6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE6" s="45"/>
+      <c r="AE6" s="50"/>
       <c r="AF6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="53"/>
+      <c r="AG6" s="42"/>
+      <c r="AH6" s="58"/>
       <c r="AI6" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -5434,7 +4979,7 @@
       <c r="D7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="40"/>
+      <c r="E7" s="42"/>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5453,7 +4998,7 @@
       <c r="K7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="40"/>
+      <c r="L7" s="42"/>
       <c r="M7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5472,7 +5017,7 @@
       <c r="R7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S7" s="40"/>
+      <c r="S7" s="42"/>
       <c r="T7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5491,7 +5036,7 @@
       <c r="Y7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z7" s="40"/>
+      <c r="Z7" s="42"/>
       <c r="AA7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5504,12 +5049,12 @@
       <c r="AD7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE7" s="45"/>
+      <c r="AE7" s="50"/>
       <c r="AF7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="40"/>
-      <c r="AH7" s="53"/>
+      <c r="AG7" s="42"/>
+      <c r="AH7" s="58"/>
       <c r="AI7" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -5546,7 +5091,7 @@
       <c r="D8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="42"/>
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5565,7 +5110,7 @@
       <c r="K8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="40"/>
+      <c r="L8" s="42"/>
       <c r="M8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5584,7 +5129,7 @@
       <c r="R8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S8" s="40"/>
+      <c r="S8" s="42"/>
       <c r="T8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5603,7 +5148,7 @@
       <c r="Y8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z8" s="40"/>
+      <c r="Z8" s="42"/>
       <c r="AA8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5616,12 +5161,12 @@
       <c r="AD8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE8" s="45"/>
+      <c r="AE8" s="50"/>
       <c r="AF8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG8" s="40"/>
-      <c r="AH8" s="53"/>
+      <c r="AG8" s="42"/>
+      <c r="AH8" s="58"/>
       <c r="AI8" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -5658,7 +5203,7 @@
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="40"/>
+      <c r="E9" s="42"/>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5677,7 +5222,7 @@
       <c r="K9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L9" s="40"/>
+      <c r="L9" s="42"/>
       <c r="M9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5696,7 +5241,7 @@
       <c r="R9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S9" s="40"/>
+      <c r="S9" s="42"/>
       <c r="T9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5715,7 +5260,7 @@
       <c r="Y9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z9" s="40"/>
+      <c r="Z9" s="42"/>
       <c r="AA9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5728,12 +5273,12 @@
       <c r="AD9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE9" s="45"/>
+      <c r="AE9" s="50"/>
       <c r="AF9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG9" s="40"/>
-      <c r="AH9" s="53"/>
+      <c r="AG9" s="42"/>
+      <c r="AH9" s="58"/>
       <c r="AI9" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -5770,7 +5315,7 @@
       <c r="D10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="40"/>
+      <c r="E10" s="42"/>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5789,7 +5334,7 @@
       <c r="K10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="40"/>
+      <c r="L10" s="42"/>
       <c r="M10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5808,7 +5353,7 @@
       <c r="R10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S10" s="40"/>
+      <c r="S10" s="42"/>
       <c r="T10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5827,7 +5372,7 @@
       <c r="Y10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z10" s="40"/>
+      <c r="Z10" s="42"/>
       <c r="AA10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5840,12 +5385,12 @@
       <c r="AD10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE10" s="45"/>
+      <c r="AE10" s="50"/>
       <c r="AF10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG10" s="40"/>
-      <c r="AH10" s="53"/>
+      <c r="AG10" s="42"/>
+      <c r="AH10" s="58"/>
       <c r="AI10" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -5882,7 +5427,7 @@
       <c r="D11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="40"/>
+      <c r="E11" s="42"/>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5901,7 +5446,7 @@
       <c r="K11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="40"/>
+      <c r="L11" s="42"/>
       <c r="M11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5920,7 +5465,7 @@
       <c r="R11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="40"/>
+      <c r="S11" s="42"/>
       <c r="T11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5939,7 +5484,7 @@
       <c r="Y11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z11" s="40"/>
+      <c r="Z11" s="42"/>
       <c r="AA11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5952,12 +5497,12 @@
       <c r="AD11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE11" s="45"/>
+      <c r="AE11" s="50"/>
       <c r="AF11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="53"/>
+      <c r="AG11" s="42"/>
+      <c r="AH11" s="58"/>
       <c r="AI11" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -5994,7 +5539,7 @@
       <c r="D12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="29"/>
+      <c r="E12" s="43"/>
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
@@ -6013,7 +5558,7 @@
       <c r="K12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="29"/>
+      <c r="L12" s="43"/>
       <c r="M12" s="4" t="s">
         <v>24</v>
       </c>
@@ -6032,7 +5577,7 @@
       <c r="R12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="S12" s="29"/>
+      <c r="S12" s="43"/>
       <c r="T12" s="4" t="s">
         <v>24</v>
       </c>
@@ -6051,7 +5596,7 @@
       <c r="Y12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z12" s="29"/>
+      <c r="Z12" s="43"/>
       <c r="AA12" s="4" t="s">
         <v>24</v>
       </c>
@@ -6064,12 +5609,12 @@
       <c r="AD12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AE12" s="46"/>
+      <c r="AE12" s="51"/>
       <c r="AF12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="50"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="55"/>
       <c r="AI12" s="3">
         <f t="shared" ref="AI12" si="5">COUNTIF(D12:AH12,"P")</f>
         <v>2</v>
@@ -6105,7 +5650,7 @@
       <c r="D13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="41"/>
+      <c r="E13" s="44"/>
       <c r="F13" s="6" t="s">
         <v>6</v>
       </c>
@@ -6124,7 +5669,7 @@
       <c r="K13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L13" s="41"/>
+      <c r="L13" s="44"/>
       <c r="M13" s="6" t="s">
         <v>6</v>
       </c>
@@ -6143,7 +5688,7 @@
       <c r="R13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S13" s="41"/>
+      <c r="S13" s="44"/>
       <c r="T13" s="6" t="s">
         <v>6</v>
       </c>
@@ -6162,7 +5707,7 @@
       <c r="Y13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Z13" s="41"/>
+      <c r="Z13" s="44"/>
       <c r="AA13" s="6" t="s">
         <v>6</v>
       </c>
@@ -6175,12 +5720,12 @@
       <c r="AD13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AE13" s="47"/>
+      <c r="AE13" s="52"/>
       <c r="AF13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AG13" s="41"/>
-      <c r="AH13" s="54"/>
+      <c r="AG13" s="44"/>
+      <c r="AH13" s="59"/>
       <c r="AI13" s="5">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -6206,55 +5751,55 @@
     </row>
     <row r="14" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="33"/>
-      <c r="AE15" s="33"/>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="33"/>
-      <c r="AH15" s="33"/>
-      <c r="AI15" s="33"/>
-      <c r="AJ15" s="33"/>
-      <c r="AK15" s="33"/>
-      <c r="AL15" s="33"/>
-      <c r="AM15" s="33"/>
-      <c r="AN15" s="34"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="35"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="35"/>
+      <c r="AJ15" s="35"/>
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="35"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="36"/>
     </row>
     <row r="16" spans="1:40" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
+      <c r="A16" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="15" t="str">
         <f>TEXT(D17,"ddd")</f>
         <v>Sat</v>
@@ -6382,11 +5927,11 @@
       <c r="AI16" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AJ16" s="37"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="37"/>
-      <c r="AM16" s="37"/>
-      <c r="AN16" s="38"/>
+      <c r="AJ16" s="40"/>
+      <c r="AK16" s="40"/>
+      <c r="AL16" s="40"/>
+      <c r="AM16" s="40"/>
+      <c r="AN16" s="41"/>
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -6524,7 +6069,7 @@
       <c r="D18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -6545,7 +6090,7 @@
       <c r="K18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L18" s="29" t="s">
+      <c r="L18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="M18" s="4" t="s">
@@ -6566,7 +6111,7 @@
       <c r="R18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S18" s="29" t="s">
+      <c r="S18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="T18" s="4" t="s">
@@ -6587,7 +6132,7 @@
       <c r="Y18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z18" s="29" t="s">
+      <c r="Z18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="AA18" s="4" t="s">
@@ -6602,16 +6147,16 @@
       <c r="AD18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE18" s="46" t="s">
+      <c r="AE18" s="51" t="s">
         <v>43</v>
       </c>
       <c r="AF18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG18" s="29" t="s">
+      <c r="AG18" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="AH18" s="50" t="s">
+      <c r="AH18" s="55" t="s">
         <v>44</v>
       </c>
       <c r="AI18" s="24">
@@ -6651,7 +6196,7 @@
       <c r="D19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="30"/>
+      <c r="E19" s="45"/>
       <c r="F19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6670,7 +6215,7 @@
       <c r="K19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L19" s="30"/>
+      <c r="L19" s="45"/>
       <c r="M19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6689,7 +6234,7 @@
       <c r="R19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S19" s="30"/>
+      <c r="S19" s="45"/>
       <c r="T19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6708,7 +6253,7 @@
       <c r="Y19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z19" s="30"/>
+      <c r="Z19" s="45"/>
       <c r="AA19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6721,12 +6266,12 @@
       <c r="AD19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE19" s="48"/>
+      <c r="AE19" s="53"/>
       <c r="AF19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="51"/>
+      <c r="AG19" s="45"/>
+      <c r="AH19" s="56"/>
       <c r="AI19" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6764,7 +6309,7 @@
       <c r="D20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="30"/>
+      <c r="E20" s="45"/>
       <c r="F20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6783,7 +6328,7 @@
       <c r="K20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L20" s="30"/>
+      <c r="L20" s="45"/>
       <c r="M20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6802,7 +6347,7 @@
       <c r="R20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S20" s="30"/>
+      <c r="S20" s="45"/>
       <c r="T20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6821,7 +6366,7 @@
       <c r="Y20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z20" s="30"/>
+      <c r="Z20" s="45"/>
       <c r="AA20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6834,12 +6379,12 @@
       <c r="AD20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE20" s="48"/>
+      <c r="AE20" s="53"/>
       <c r="AF20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="51"/>
+      <c r="AG20" s="45"/>
+      <c r="AH20" s="56"/>
       <c r="AI20" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6877,7 +6422,7 @@
       <c r="D21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="30"/>
+      <c r="E21" s="45"/>
       <c r="F21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6896,7 +6441,7 @@
       <c r="K21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="30"/>
+      <c r="L21" s="45"/>
       <c r="M21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6915,7 +6460,7 @@
       <c r="R21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S21" s="30"/>
+      <c r="S21" s="45"/>
       <c r="T21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6934,7 +6479,7 @@
       <c r="Y21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z21" s="30"/>
+      <c r="Z21" s="45"/>
       <c r="AA21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6947,12 +6492,12 @@
       <c r="AD21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE21" s="48"/>
+      <c r="AE21" s="53"/>
       <c r="AF21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG21" s="30"/>
-      <c r="AH21" s="51"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="56"/>
       <c r="AI21" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6990,7 +6535,7 @@
       <c r="D22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="30"/>
+      <c r="E22" s="45"/>
       <c r="F22" s="4" t="s">
         <v>6</v>
       </c>
@@ -7009,7 +6554,7 @@
       <c r="K22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="30"/>
+      <c r="L22" s="45"/>
       <c r="M22" s="4" t="s">
         <v>6</v>
       </c>
@@ -7028,7 +6573,7 @@
       <c r="R22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S22" s="30"/>
+      <c r="S22" s="45"/>
       <c r="T22" s="4" t="s">
         <v>6</v>
       </c>
@@ -7047,7 +6592,7 @@
       <c r="Y22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z22" s="30"/>
+      <c r="Z22" s="45"/>
       <c r="AA22" s="4" t="s">
         <v>6</v>
       </c>
@@ -7060,12 +6605,12 @@
       <c r="AD22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE22" s="48"/>
+      <c r="AE22" s="53"/>
       <c r="AF22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="51"/>
+      <c r="AG22" s="45"/>
+      <c r="AH22" s="56"/>
       <c r="AI22" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -7103,7 +6648,7 @@
       <c r="D23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="30"/>
+      <c r="E23" s="45"/>
       <c r="F23" s="4" t="s">
         <v>6</v>
       </c>
@@ -7122,7 +6667,7 @@
       <c r="K23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L23" s="30"/>
+      <c r="L23" s="45"/>
       <c r="M23" s="4" t="s">
         <v>6</v>
       </c>
@@ -7141,7 +6686,7 @@
       <c r="R23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S23" s="30"/>
+      <c r="S23" s="45"/>
       <c r="T23" s="4" t="s">
         <v>6</v>
       </c>
@@ -7160,7 +6705,7 @@
       <c r="Y23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z23" s="30"/>
+      <c r="Z23" s="45"/>
       <c r="AA23" s="4" t="s">
         <v>6</v>
       </c>
@@ -7173,12 +6718,12 @@
       <c r="AD23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE23" s="48"/>
+      <c r="AE23" s="53"/>
       <c r="AF23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="51"/>
+      <c r="AG23" s="45"/>
+      <c r="AH23" s="56"/>
       <c r="AI23" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -7216,7 +6761,7 @@
       <c r="D24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="30"/>
+      <c r="E24" s="45"/>
       <c r="F24" s="11" t="s">
         <v>6</v>
       </c>
@@ -7235,7 +6780,7 @@
       <c r="K24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L24" s="30"/>
+      <c r="L24" s="45"/>
       <c r="M24" s="11" t="s">
         <v>6</v>
       </c>
@@ -7254,7 +6799,7 @@
       <c r="R24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S24" s="30"/>
+      <c r="S24" s="45"/>
       <c r="T24" s="11" t="s">
         <v>6</v>
       </c>
@@ -7273,7 +6818,7 @@
       <c r="Y24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="Z24" s="30"/>
+      <c r="Z24" s="45"/>
       <c r="AA24" s="11" t="s">
         <v>6</v>
       </c>
@@ -7286,12 +6831,12 @@
       <c r="AD24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AE24" s="48"/>
+      <c r="AE24" s="53"/>
       <c r="AF24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AG24" s="30"/>
-      <c r="AH24" s="51"/>
+      <c r="AG24" s="45"/>
+      <c r="AH24" s="56"/>
       <c r="AI24" s="25">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -7329,7 +6874,7 @@
       <c r="D25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="31"/>
+      <c r="E25" s="46"/>
       <c r="F25" s="6" t="s">
         <v>6</v>
       </c>
@@ -7348,7 +6893,7 @@
       <c r="K25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L25" s="31"/>
+      <c r="L25" s="46"/>
       <c r="M25" s="6" t="s">
         <v>6</v>
       </c>
@@ -7367,7 +6912,7 @@
       <c r="R25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S25" s="31"/>
+      <c r="S25" s="46"/>
       <c r="T25" s="6" t="s">
         <v>6</v>
       </c>
@@ -7386,7 +6931,7 @@
       <c r="Y25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Z25" s="31"/>
+      <c r="Z25" s="46"/>
       <c r="AA25" s="6" t="s">
         <v>6</v>
       </c>
@@ -7399,12 +6944,12 @@
       <c r="AD25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AE25" s="49"/>
+      <c r="AE25" s="54"/>
       <c r="AF25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AG25" s="31"/>
-      <c r="AH25" s="52"/>
+      <c r="AG25" s="46"/>
+      <c r="AH25" s="57"/>
       <c r="AI25" s="26">
         <f t="shared" si="9"/>
         <v>23</v>
@@ -7430,13 +6975,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A2:AN2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="AI3:AN3"/>
-    <mergeCell ref="E5:E13"/>
-    <mergeCell ref="L5:L13"/>
-    <mergeCell ref="S5:S13"/>
-    <mergeCell ref="Z5:Z13"/>
     <mergeCell ref="AG18:AG25"/>
     <mergeCell ref="AG5:AG13"/>
     <mergeCell ref="AE5:AE13"/>
@@ -7450,160 +6988,167 @@
     <mergeCell ref="L18:L25"/>
     <mergeCell ref="S18:S25"/>
     <mergeCell ref="Z18:Z25"/>
+    <mergeCell ref="A2:AN2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="E5:E13"/>
+    <mergeCell ref="L5:L13"/>
+    <mergeCell ref="S5:S13"/>
+    <mergeCell ref="Z5:Z13"/>
   </mergeCells>
   <conditionalFormatting sqref="D18:D25">
-    <cfRule type="expression" dxfId="209" priority="123">
+    <cfRule type="expression" dxfId="157" priority="123">
       <formula>D$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="124" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="125" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="155" priority="124" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="125" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:AH13">
-    <cfRule type="cellIs" dxfId="206" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="8" operator="equal">
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:AH25">
-    <cfRule type="cellIs" dxfId="205" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5 L5 S5 Z5 AG5 D5:D13 F5:K13 M5:R13 T5:Y13 AA5:AF13 AH5:AH13 D3:AH4 D16:AH17">
-    <cfRule type="expression" dxfId="204" priority="126">
+    <cfRule type="expression" dxfId="152" priority="126">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5 L5 S5 Z5 AG5 D5:D13 F5:K13 M5:R13 T5:Y13 AA5:AF13 AH5:AH13">
-    <cfRule type="cellIs" dxfId="203" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="128" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="127" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="128" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18">
-    <cfRule type="expression" dxfId="201" priority="120">
+    <cfRule type="cellIs" dxfId="149" priority="122" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="121" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="147" priority="120">
       <formula>E$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="200" priority="121" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="122" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:K25">
-    <cfRule type="expression" dxfId="198" priority="66">
+    <cfRule type="expression" dxfId="146" priority="66">
       <formula>F$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="68" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="144" priority="67" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="68" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
-    <cfRule type="expression" dxfId="195" priority="114">
+    <cfRule type="cellIs" dxfId="143" priority="116" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="115" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="141" priority="114">
       <formula>L$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="194" priority="115" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="116" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:R25">
-    <cfRule type="expression" dxfId="192" priority="48">
+    <cfRule type="cellIs" dxfId="140" priority="49" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="50" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="138" priority="48">
       <formula>M$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="49" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="50" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18">
-    <cfRule type="expression" dxfId="189" priority="111">
+    <cfRule type="cellIs" dxfId="137" priority="113" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="112" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="135" priority="111">
       <formula>S$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="112" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="113" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:Y25">
-    <cfRule type="expression" dxfId="186" priority="30">
+    <cfRule type="expression" dxfId="134" priority="30">
       <formula>T$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="31" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="32" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z18">
-    <cfRule type="expression" dxfId="183" priority="90">
+    <cfRule type="expression" dxfId="131" priority="90">
       <formula>Z$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="91" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="91" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="92" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA18:AD25">
-    <cfRule type="expression" dxfId="180" priority="18">
+    <cfRule type="cellIs" dxfId="128" priority="20" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="19" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="126" priority="18">
       <formula>AA$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="19" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="20" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE18">
-    <cfRule type="expression" dxfId="177" priority="5">
+    <cfRule type="cellIs" dxfId="125" priority="7" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="6" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="123" priority="5">
       <formula>AE$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="176" priority="6" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="7" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18:AF25">
-    <cfRule type="expression" dxfId="174" priority="12">
+    <cfRule type="cellIs" dxfId="122" priority="14" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="13" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="120" priority="12">
       <formula>AF$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="13" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="14" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG18:AH18">
-    <cfRule type="expression" dxfId="171" priority="2">
+    <cfRule type="cellIs" dxfId="119" priority="4" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="3" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="117" priority="2">
       <formula>AG$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="170" priority="3" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="4" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7631,54 +7176,54 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
-      <c r="AK2" s="33"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="36"/>
     </row>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
+      <c r="A3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="15" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
@@ -7802,11 +7347,11 @@
       <c r="AH3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AI3" s="37"/>
-      <c r="AJ3" s="37"/>
-      <c r="AK3" s="37"/>
-      <c r="AL3" s="37"/>
-      <c r="AM3" s="38"/>
+      <c r="AI3" s="40"/>
+      <c r="AJ3" s="40"/>
+      <c r="AK3" s="40"/>
+      <c r="AL3" s="40"/>
+      <c r="AM3" s="41"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -7937,22 +7482,22 @@
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="58" t="s">
         <v>44</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="60" t="s">
         <v>45</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="4" t="s">
@@ -7973,7 +7518,7 @@
       <c r="O5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="40" t="s">
+      <c r="P5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="Q5" s="4" t="s">
@@ -7994,7 +7539,7 @@
       <c r="V5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W5" s="40" t="s">
+      <c r="W5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="X5" s="4" t="s">
@@ -8015,7 +7560,7 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="40" t="s">
+      <c r="AD5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="AE5" s="4" t="s">
@@ -8028,15 +7573,15 @@
         <v>6</v>
       </c>
       <c r="AH5" s="3">
-        <f>COUNTIF(D5:AG5,"P")</f>
+        <f t="shared" ref="AH5:AH13" si="1">COUNTIF(D5:AG5,"P")</f>
         <v>22</v>
       </c>
       <c r="AI5" s="4">
-        <f>COUNTIF(D5:AG5,"A")</f>
+        <f t="shared" ref="AI5:AI13" si="2">COUNTIF(D5:AG5,"A")</f>
         <v>0</v>
       </c>
       <c r="AJ5" s="4">
-        <f>COUNTIF(D5:AG5,"L")</f>
+        <f t="shared" ref="AJ5:AJ13" si="3">COUNTIF(D5:AG5,"L")</f>
         <v>1</v>
       </c>
       <c r="AK5" s="4">
@@ -8046,7 +7591,7 @@
         <v>4</v>
       </c>
       <c r="AM5" s="16">
-        <f>AH5+AJ5+AK5+AL5</f>
+        <f t="shared" ref="AM5:AM12" si="4">AH5+AJ5+AK5+AL5</f>
         <v>30</v>
       </c>
     </row>
@@ -8060,16 +7605,16 @@
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="55"/>
+      <c r="G6" s="60"/>
       <c r="H6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="40"/>
+      <c r="I6" s="42"/>
       <c r="J6" s="4" t="s">
         <v>6</v>
       </c>
@@ -8088,7 +7633,7 @@
       <c r="O6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="40"/>
+      <c r="P6" s="42"/>
       <c r="Q6" s="4" t="s">
         <v>6</v>
       </c>
@@ -8107,7 +7652,7 @@
       <c r="V6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="40"/>
+      <c r="W6" s="42"/>
       <c r="X6" s="4" t="s">
         <v>6</v>
       </c>
@@ -8126,7 +7671,7 @@
       <c r="AC6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD6" s="40"/>
+      <c r="AD6" s="42"/>
       <c r="AE6" s="4" t="s">
         <v>6</v>
       </c>
@@ -8137,15 +7682,15 @@
         <v>6</v>
       </c>
       <c r="AH6" s="3">
-        <f>COUNTIF(D6:AG6,"P")</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="AI6" s="4">
-        <f>COUNTIF(D6:AG6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ6" s="4">
-        <f>COUNTIF(D6:AG6,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK6" s="4">
@@ -8155,7 +7700,7 @@
         <v>4</v>
       </c>
       <c r="AM6" s="16">
-        <f>AH6+AJ6+AK6+AL6</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
     </row>
@@ -8169,16 +7714,16 @@
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="55"/>
+      <c r="G7" s="60"/>
       <c r="H7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="40"/>
+      <c r="I7" s="42"/>
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
@@ -8197,7 +7742,7 @@
       <c r="O7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P7" s="40"/>
+      <c r="P7" s="42"/>
       <c r="Q7" s="4" t="s">
         <v>6</v>
       </c>
@@ -8216,7 +7761,7 @@
       <c r="V7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="40"/>
+      <c r="W7" s="42"/>
       <c r="X7" s="4" t="s">
         <v>6</v>
       </c>
@@ -8235,7 +7780,7 @@
       <c r="AC7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD7" s="40"/>
+      <c r="AD7" s="42"/>
       <c r="AE7" s="4" t="s">
         <v>6</v>
       </c>
@@ -8246,15 +7791,15 @@
         <v>6</v>
       </c>
       <c r="AH7" s="3">
-        <f>COUNTIF(D7:AG7,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AI7" s="4">
-        <f>COUNTIF(D7:AG7,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ7" s="4">
-        <f>COUNTIF(D7:AG7,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AK7" s="4">
@@ -8264,7 +7809,7 @@
         <v>4</v>
       </c>
       <c r="AM7" s="16">
-        <f>AH7+AJ7+AK7+AL7</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
     </row>
@@ -8278,16 +7823,16 @@
       <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
       <c r="F8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="55"/>
+      <c r="G8" s="60"/>
       <c r="H8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="40"/>
+      <c r="I8" s="42"/>
       <c r="J8" s="4" t="s">
         <v>6</v>
       </c>
@@ -8306,7 +7851,7 @@
       <c r="O8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P8" s="40"/>
+      <c r="P8" s="42"/>
       <c r="Q8" s="4" t="s">
         <v>6</v>
       </c>
@@ -8325,7 +7870,7 @@
       <c r="V8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W8" s="40"/>
+      <c r="W8" s="42"/>
       <c r="X8" s="4" t="s">
         <v>6</v>
       </c>
@@ -8344,7 +7889,7 @@
       <c r="AC8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD8" s="40"/>
+      <c r="AD8" s="42"/>
       <c r="AE8" s="4" t="s">
         <v>6</v>
       </c>
@@ -8355,15 +7900,15 @@
         <v>6</v>
       </c>
       <c r="AH8" s="3">
-        <f>COUNTIF(D8:AG8,"P")</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="AI8" s="4">
-        <f>COUNTIF(D8:AG8,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AJ8" s="4">
-        <f>COUNTIF(D8:AG8,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK8" s="4">
@@ -8373,7 +7918,7 @@
         <v>4</v>
       </c>
       <c r="AM8" s="16">
-        <f>AH8+AJ8+AK8+AL8</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
     </row>
@@ -8387,16 +7932,16 @@
       <c r="C9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="55"/>
+      <c r="G9" s="60"/>
       <c r="H9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="40"/>
+      <c r="I9" s="42"/>
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
@@ -8415,7 +7960,7 @@
       <c r="O9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P9" s="40"/>
+      <c r="P9" s="42"/>
       <c r="Q9" s="4" t="s">
         <v>6</v>
       </c>
@@ -8434,7 +7979,7 @@
       <c r="V9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W9" s="40"/>
+      <c r="W9" s="42"/>
       <c r="X9" s="4" t="s">
         <v>6</v>
       </c>
@@ -8453,7 +7998,7 @@
       <c r="AC9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="40"/>
+      <c r="AD9" s="42"/>
       <c r="AE9" s="4" t="s">
         <v>6</v>
       </c>
@@ -8464,15 +8009,15 @@
         <v>6</v>
       </c>
       <c r="AH9" s="3">
-        <f>COUNTIF(D9:AG9,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AI9" s="4">
-        <f>COUNTIF(D9:AG9,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ9" s="4">
-        <f>COUNTIF(D9:AG9,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AK9" s="4">
@@ -8482,7 +8027,7 @@
         <v>4</v>
       </c>
       <c r="AM9" s="16">
-        <f>AH9+AJ9+AK9+AL9</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
     </row>
@@ -8496,16 +8041,16 @@
       <c r="C10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="55"/>
+      <c r="G10" s="60"/>
       <c r="H10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="40"/>
+      <c r="I10" s="42"/>
       <c r="J10" s="4" t="s">
         <v>6</v>
       </c>
@@ -8524,7 +8069,7 @@
       <c r="O10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="40"/>
+      <c r="P10" s="42"/>
       <c r="Q10" s="4" t="s">
         <v>6</v>
       </c>
@@ -8543,7 +8088,7 @@
       <c r="V10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W10" s="40"/>
+      <c r="W10" s="42"/>
       <c r="X10" s="4" t="s">
         <v>6</v>
       </c>
@@ -8562,7 +8107,7 @@
       <c r="AC10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD10" s="40"/>
+      <c r="AD10" s="42"/>
       <c r="AE10" s="4" t="s">
         <v>6</v>
       </c>
@@ -8573,15 +8118,15 @@
         <v>6</v>
       </c>
       <c r="AH10" s="3">
-        <f>COUNTIF(D10:AG10,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AI10" s="4">
-        <f>COUNTIF(D10:AG10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ10" s="4">
-        <f>COUNTIF(D10:AG10,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AK10" s="4">
@@ -8591,7 +8136,7 @@
         <v>4</v>
       </c>
       <c r="AM10" s="16">
-        <f>AH10+AJ10+AK10+AL10</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
     </row>
@@ -8605,16 +8150,16 @@
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="55"/>
+      <c r="G11" s="60"/>
       <c r="H11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="40"/>
+      <c r="I11" s="42"/>
       <c r="J11" s="4" t="s">
         <v>6</v>
       </c>
@@ -8633,7 +8178,7 @@
       <c r="O11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P11" s="40"/>
+      <c r="P11" s="42"/>
       <c r="Q11" s="4" t="s">
         <v>6</v>
       </c>
@@ -8652,7 +8197,7 @@
       <c r="V11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W11" s="40"/>
+      <c r="W11" s="42"/>
       <c r="X11" s="4" t="s">
         <v>6</v>
       </c>
@@ -8671,7 +8216,7 @@
       <c r="AC11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD11" s="40"/>
+      <c r="AD11" s="42"/>
       <c r="AE11" s="4" t="s">
         <v>6</v>
       </c>
@@ -8682,15 +8227,15 @@
         <v>6</v>
       </c>
       <c r="AH11" s="3">
-        <f>COUNTIF(D11:AG11,"P")</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="AI11" s="4">
-        <f>COUNTIF(D11:AG11,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ11" s="4">
-        <f>COUNTIF(D11:AG11,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK11" s="4">
@@ -8700,28 +8245,30 @@
         <v>4</v>
       </c>
       <c r="AM11" s="16">
-        <f>AH11+AJ11+AK11+AL11</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
+      <c r="A12" s="10">
+        <v>8</v>
+      </c>
       <c r="B12" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="56"/>
+      <c r="G12" s="61"/>
       <c r="H12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="29"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8740,7 +8287,7 @@
       <c r="O12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="P12" s="29"/>
+      <c r="P12" s="43"/>
       <c r="Q12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8759,7 +8306,7 @@
       <c r="V12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W12" s="29"/>
+      <c r="W12" s="43"/>
       <c r="X12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8778,7 +8325,7 @@
       <c r="AC12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="AD12" s="29"/>
+      <c r="AD12" s="43"/>
       <c r="AE12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8789,15 +8336,15 @@
         <v>6</v>
       </c>
       <c r="AH12" s="3">
-        <f>COUNTIF(D12:AG12,"P")</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="AI12" s="4">
-        <f>COUNTIF(D12:AG12,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AJ12" s="4">
-        <f>COUNTIF(D12:AG12,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AK12" s="4">
@@ -8807,7 +8354,7 @@
         <v>4</v>
       </c>
       <c r="AM12" s="16">
-        <f>AH12+AJ12+AK12+AL12</f>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
     </row>
@@ -8821,16 +8368,16 @@
       <c r="C13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
       <c r="F13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="57"/>
+      <c r="G13" s="62"/>
       <c r="H13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="41"/>
+      <c r="I13" s="44"/>
       <c r="J13" s="6" t="s">
         <v>24</v>
       </c>
@@ -8849,7 +8396,7 @@
       <c r="O13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="P13" s="41"/>
+      <c r="P13" s="44"/>
       <c r="Q13" s="6" t="s">
         <v>24</v>
       </c>
@@ -8868,7 +8415,7 @@
       <c r="V13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="W13" s="41"/>
+      <c r="W13" s="44"/>
       <c r="X13" s="6" t="s">
         <v>24</v>
       </c>
@@ -8887,7 +8434,7 @@
       <c r="AC13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AD13" s="41"/>
+      <c r="AD13" s="44"/>
       <c r="AE13" s="6" t="s">
         <v>6</v>
       </c>
@@ -8898,15 +8445,15 @@
         <v>6</v>
       </c>
       <c r="AH13" s="5">
-        <f>COUNTIF(D13:AG13,"P")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="AI13" s="6">
-        <f>COUNTIF(D13:AG13,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ13" s="6">
-        <f>COUNTIF(D13:AG13,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK13" s="6">
@@ -8921,182 +8468,182 @@
     </row>
     <row r="14" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="33"/>
-      <c r="AE15" s="33"/>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="33"/>
-      <c r="AH15" s="33"/>
-      <c r="AI15" s="33"/>
-      <c r="AJ15" s="33"/>
-      <c r="AK15" s="33"/>
-      <c r="AL15" s="33"/>
-      <c r="AM15" s="34"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="35"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="35"/>
+      <c r="AJ15" s="35"/>
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="35"/>
+      <c r="AM15" s="36"/>
     </row>
     <row r="16" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
+      <c r="A16" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="15" t="str">
         <f>TEXT(D17,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="E16" s="15" t="str">
-        <f t="shared" ref="E16:AG16" si="1">TEXT(E17,"ddd")</f>
+        <f t="shared" ref="E16:AG16" si="5">TEXT(E17,"ddd")</f>
         <v>Wed</v>
       </c>
       <c r="F16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
       <c r="G16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
       <c r="H16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
       <c r="I16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
       <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
       <c r="K16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
       <c r="L16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
       <c r="M16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
       <c r="N16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
       <c r="O16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
       <c r="P16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
       <c r="Q16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
       <c r="R16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
       <c r="S16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
       <c r="T16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
       <c r="U16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
       <c r="V16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
       <c r="W16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
       <c r="X16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
       <c r="Y16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
       <c r="Z16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
       <c r="AA16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
       <c r="AB16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
       <c r="AC16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
       <c r="AD16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
       <c r="AE16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
       <c r="AF16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
       <c r="AG16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
       <c r="AH16" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AI16" s="37"/>
-      <c r="AJ16" s="37"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="37"/>
-      <c r="AM16" s="38"/>
+      <c r="AI16" s="40"/>
+      <c r="AJ16" s="40"/>
+      <c r="AK16" s="40"/>
+      <c r="AL16" s="40"/>
+      <c r="AM16" s="41"/>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -9228,22 +8775,22 @@
       <c r="C18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="D18" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="58" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="60" t="s">
         <v>45</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="29" t="s">
+      <c r="I18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -9264,7 +8811,7 @@
       <c r="O18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P18" s="29" t="s">
+      <c r="P18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="Q18" s="4" t="s">
@@ -9285,7 +8832,7 @@
       <c r="V18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W18" s="29" t="s">
+      <c r="W18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="X18" s="4" t="s">
@@ -9306,7 +8853,7 @@
       <c r="AC18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD18" s="29" t="s">
+      <c r="AD18" s="43" t="s">
         <v>26</v>
       </c>
       <c r="AE18" s="4" t="s">
@@ -9319,15 +8866,15 @@
         <v>6</v>
       </c>
       <c r="AH18" s="24">
-        <f>COUNTIF(D18:AG18,"P")</f>
+        <f t="shared" ref="AH18:AH25" si="6">COUNTIF(D18:AG18,"P")</f>
         <v>23</v>
       </c>
       <c r="AI18" s="8">
-        <f>COUNTIF(D18:AG18,"A")</f>
+        <f t="shared" ref="AI18:AI25" si="7">COUNTIF(D18:AG18,"A")</f>
         <v>0</v>
       </c>
       <c r="AJ18" s="8">
-        <f>COUNTIF(D18:AG18,"L")</f>
+        <f t="shared" ref="AJ18:AJ25" si="8">COUNTIF(D18:AG18,"L")</f>
         <v>0</v>
       </c>
       <c r="AK18" s="4">
@@ -9352,16 +8899,16 @@
       <c r="C19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
       <c r="F19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="55"/>
+      <c r="G19" s="60"/>
       <c r="H19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I19" s="30"/>
+      <c r="I19" s="45"/>
       <c r="J19" s="4" t="s">
         <v>6</v>
       </c>
@@ -9380,7 +8927,7 @@
       <c r="O19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P19" s="30"/>
+      <c r="P19" s="45"/>
       <c r="Q19" s="4" t="s">
         <v>6</v>
       </c>
@@ -9399,7 +8946,7 @@
       <c r="V19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W19" s="30"/>
+      <c r="W19" s="45"/>
       <c r="X19" s="4" t="s">
         <v>6</v>
       </c>
@@ -9418,7 +8965,7 @@
       <c r="AC19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD19" s="30"/>
+      <c r="AD19" s="45"/>
       <c r="AE19" s="4" t="s">
         <v>6</v>
       </c>
@@ -9429,15 +8976,15 @@
         <v>6</v>
       </c>
       <c r="AH19" s="24">
-        <f>COUNTIF(D19:AG19,"P")</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="AI19" s="8">
-        <f>COUNTIF(D19:AG19,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="8">
-        <f>COUNTIF(D19:AG19,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK19" s="4">
@@ -9447,13 +8994,13 @@
         <v>5</v>
       </c>
       <c r="AM19" s="16">
-        <f t="shared" ref="AM19:AM25" si="2">AH19+AJ19+AK19+AL19</f>
+        <f t="shared" ref="AM19:AM25" si="9">AH19+AJ19+AK19+AL19</f>
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <f t="shared" ref="A20:A25" si="3">IF(B20="","",A19+1)</f>
+        <f t="shared" ref="A20:A25" si="10">IF(B20="","",A19+1)</f>
         <v>3</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -9462,16 +9009,16 @@
       <c r="C20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
       <c r="F20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="55"/>
+      <c r="G20" s="60"/>
       <c r="H20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="30"/>
+      <c r="I20" s="45"/>
       <c r="J20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9490,7 +9037,7 @@
       <c r="O20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P20" s="30"/>
+      <c r="P20" s="45"/>
       <c r="Q20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9509,7 +9056,7 @@
       <c r="V20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W20" s="30"/>
+      <c r="W20" s="45"/>
       <c r="X20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9528,7 +9075,7 @@
       <c r="AC20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD20" s="30"/>
+      <c r="AD20" s="45"/>
       <c r="AE20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9539,15 +9086,15 @@
         <v>6</v>
       </c>
       <c r="AH20" s="24">
-        <f>COUNTIF(D20:AG20,"P")</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="AI20" s="8">
-        <f>COUNTIF(D20:AG20,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ20" s="8">
-        <f>COUNTIF(D20:AG20,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK20" s="4">
@@ -9557,13 +9104,13 @@
         <v>5</v>
       </c>
       <c r="AM20" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -9572,16 +9119,16 @@
       <c r="C21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
       <c r="F21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="55"/>
+      <c r="G21" s="60"/>
       <c r="H21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="30"/>
+      <c r="I21" s="45"/>
       <c r="J21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9600,7 +9147,7 @@
       <c r="O21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P21" s="30"/>
+      <c r="P21" s="45"/>
       <c r="Q21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9619,7 +9166,7 @@
       <c r="V21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W21" s="30"/>
+      <c r="W21" s="45"/>
       <c r="X21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9638,7 +9185,7 @@
       <c r="AC21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD21" s="30"/>
+      <c r="AD21" s="45"/>
       <c r="AE21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9649,15 +9196,15 @@
         <v>6</v>
       </c>
       <c r="AH21" s="24">
-        <f>COUNTIF(D21:AG21,"P")</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="AI21" s="8">
-        <f>COUNTIF(D21:AG21,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ21" s="8">
-        <f>COUNTIF(D21:AG21,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK21" s="4">
@@ -9667,13 +9214,13 @@
         <v>5</v>
       </c>
       <c r="AM21" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -9682,16 +9229,16 @@
       <c r="C22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
       <c r="F22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="55"/>
+      <c r="G22" s="60"/>
       <c r="H22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="30"/>
+      <c r="I22" s="45"/>
       <c r="J22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9710,7 +9257,7 @@
       <c r="O22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P22" s="30"/>
+      <c r="P22" s="45"/>
       <c r="Q22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9729,7 +9276,7 @@
       <c r="V22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W22" s="30"/>
+      <c r="W22" s="45"/>
       <c r="X22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9748,7 +9295,7 @@
       <c r="AC22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD22" s="30"/>
+      <c r="AD22" s="45"/>
       <c r="AE22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9759,15 +9306,15 @@
         <v>6</v>
       </c>
       <c r="AH22" s="24">
-        <f>COUNTIF(D22:AG22,"P")</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="AI22" s="8">
-        <f>COUNTIF(D22:AG22,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ22" s="8">
-        <f>COUNTIF(D22:AG22,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK22" s="4">
@@ -9777,13 +9324,13 @@
         <v>5</v>
       </c>
       <c r="AM22" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="B23" s="11" t="s">
@@ -9792,16 +9339,16 @@
       <c r="C23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
       <c r="F23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="55"/>
+      <c r="G23" s="60"/>
       <c r="H23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="30"/>
+      <c r="I23" s="45"/>
       <c r="J23" s="4" t="s">
         <v>6</v>
       </c>
@@ -9820,7 +9367,7 @@
       <c r="O23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P23" s="30"/>
+      <c r="P23" s="45"/>
       <c r="Q23" s="4" t="s">
         <v>6</v>
       </c>
@@ -9839,7 +9386,7 @@
       <c r="V23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W23" s="30"/>
+      <c r="W23" s="45"/>
       <c r="X23" s="4" t="s">
         <v>6</v>
       </c>
@@ -9858,7 +9405,7 @@
       <c r="AC23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD23" s="30"/>
+      <c r="AD23" s="45"/>
       <c r="AE23" s="4" t="s">
         <v>6</v>
       </c>
@@ -9869,15 +9416,15 @@
         <v>6</v>
       </c>
       <c r="AH23" s="24">
-        <f>COUNTIF(D23:AG23,"P")</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="AI23" s="8">
-        <f>COUNTIF(D23:AG23,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="8">
-        <f>COUNTIF(D23:AG23,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK23" s="4">
@@ -9887,13 +9434,13 @@
         <v>5</v>
       </c>
       <c r="AM23" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -9902,16 +9449,16 @@
       <c r="C24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
       <c r="F24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="55"/>
+      <c r="G24" s="60"/>
       <c r="H24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="30"/>
+      <c r="I24" s="45"/>
       <c r="J24" s="11" t="s">
         <v>6</v>
       </c>
@@ -9930,7 +9477,7 @@
       <c r="O24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P24" s="30"/>
+      <c r="P24" s="45"/>
       <c r="Q24" s="11" t="s">
         <v>6</v>
       </c>
@@ -9949,7 +9496,7 @@
       <c r="V24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="W24" s="30"/>
+      <c r="W24" s="45"/>
       <c r="X24" s="11" t="s">
         <v>6</v>
       </c>
@@ -9968,7 +9515,7 @@
       <c r="AC24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AD24" s="30"/>
+      <c r="AD24" s="45"/>
       <c r="AE24" s="11" t="s">
         <v>6</v>
       </c>
@@ -9979,15 +9526,15 @@
         <v>6</v>
       </c>
       <c r="AH24" s="25">
-        <f>COUNTIF(D24:AG24,"P")</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="AI24" s="12">
-        <f>COUNTIF(D24:AG24,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ24" s="8">
-        <f>COUNTIF(D24:AG24,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK24" s="11">
@@ -9997,13 +9544,13 @@
         <v>5</v>
       </c>
       <c r="AM24" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -10012,16 +9559,16 @@
       <c r="C25" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
       <c r="F25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="57"/>
+      <c r="G25" s="62"/>
       <c r="H25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I25" s="31"/>
+      <c r="I25" s="46"/>
       <c r="J25" s="6" t="s">
         <v>6</v>
       </c>
@@ -10040,7 +9587,7 @@
       <c r="O25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="P25" s="31"/>
+      <c r="P25" s="46"/>
       <c r="Q25" s="6" t="s">
         <v>6</v>
       </c>
@@ -10059,7 +9606,7 @@
       <c r="V25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="W25" s="31"/>
+      <c r="W25" s="46"/>
       <c r="X25" s="6" t="s">
         <v>6</v>
       </c>
@@ -10078,7 +9625,7 @@
       <c r="AC25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AD25" s="31"/>
+      <c r="AD25" s="46"/>
       <c r="AE25" s="6" t="s">
         <v>6</v>
       </c>
@@ -10089,15 +9636,15 @@
         <v>6</v>
       </c>
       <c r="AH25" s="26">
-        <f>COUNTIF(D25:AG25,"P")</f>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="AI25" s="9">
-        <f>COUNTIF(D25:AG25,"A")</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AJ25" s="9">
-        <f>COUNTIF(D25:AG25,"L")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AK25" s="6">
@@ -10107,17 +9654,16 @@
         <v>5</v>
       </c>
       <c r="AM25" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D5:D13"/>
-    <mergeCell ref="G5:G13"/>
-    <mergeCell ref="D18:D25"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="G18:G25"/>
+    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="AH3:AM3"/>
+    <mergeCell ref="E5:E13"/>
     <mergeCell ref="I5:I13"/>
     <mergeCell ref="P5:P13"/>
     <mergeCell ref="W5:W13"/>
@@ -10129,349 +9675,247 @@
     <mergeCell ref="A15:AM15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="A2:AM2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="AH3:AM3"/>
-    <mergeCell ref="E5:E13"/>
+    <mergeCell ref="D5:D13"/>
+    <mergeCell ref="G5:G13"/>
+    <mergeCell ref="D18:D25"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="G18:G25"/>
   </mergeCells>
-  <conditionalFormatting sqref="AG18:AG25">
-    <cfRule type="expression" dxfId="168" priority="109">
-      <formula>AG$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="110" operator="equal">
+  <conditionalFormatting sqref="D18:E25">
+    <cfRule type="cellIs" dxfId="116" priority="5" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:F25">
+    <cfRule type="cellIs" dxfId="115" priority="7" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="111" operator="equal">
+    <cfRule type="expression" dxfId="114" priority="6">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="113" priority="8" operator="equal">
       <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:AG13 AM13 D16:AG17">
+    <cfRule type="expression" dxfId="112" priority="112">
+      <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:AG13 AM13">
-    <cfRule type="cellIs" dxfId="165" priority="81" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="114" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="113" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="81" operator="equal">
       <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F25 H18:AG25">
-    <cfRule type="cellIs" dxfId="164" priority="74" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16:AG17 D3:AG13 AM13">
-    <cfRule type="expression" dxfId="163" priority="112">
-      <formula>D$3="SUN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:AG13 AM13">
-    <cfRule type="cellIs" dxfId="162" priority="113" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="114" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F25 H18:K25">
-    <cfRule type="expression" dxfId="157" priority="94">
+    <cfRule type="cellIs" dxfId="108" priority="96" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="107" priority="95" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="94">
       <formula>F$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="95" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18:G25">
+    <cfRule type="expression" dxfId="105" priority="2">
+      <formula>G$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="3" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="96" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="4" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18:AG25 F18:F25">
+    <cfRule type="cellIs" dxfId="101" priority="74" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I18">
+    <cfRule type="cellIs" dxfId="100" priority="68" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="67">
+      <formula>I$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="69" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J18:L25">
+    <cfRule type="expression" dxfId="97" priority="43">
+      <formula>J$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="44" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="95" priority="45" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
-    <cfRule type="expression" dxfId="154" priority="103">
+    <cfRule type="expression" dxfId="94" priority="103">
       <formula>L$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="104" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="104" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="105" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="105" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:R25">
-    <cfRule type="expression" dxfId="151" priority="91">
+    <cfRule type="cellIs" dxfId="91" priority="93" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="92" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="91">
       <formula>M$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="92" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P18">
+    <cfRule type="cellIs" dxfId="88" priority="66" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="65" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="93" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="86" priority="64">
+      <formula>P$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18">
-    <cfRule type="expression" dxfId="148" priority="100">
+    <cfRule type="expression" dxfId="85" priority="100">
       <formula>S$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="101" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="102" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="101" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="102" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S18:S25">
+    <cfRule type="expression" dxfId="82" priority="40">
+      <formula>S$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="42" operator="equal">
       <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="41" operator="equal">
+      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:Y25">
-    <cfRule type="expression" dxfId="145" priority="88">
+    <cfRule type="cellIs" dxfId="79" priority="90" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="88">
       <formula>T$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="89" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="90" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W18">
+    <cfRule type="cellIs" dxfId="76" priority="62" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="61">
+      <formula>W$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="63" operator="equal">
       <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X18:Z25">
+    <cfRule type="cellIs" dxfId="73" priority="33" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="32" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="31">
+      <formula>X$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z18">
-    <cfRule type="expression" dxfId="142" priority="97">
+    <cfRule type="expression" dxfId="70" priority="97">
       <formula>Z$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="98" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="99" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="99" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA18:AD25">
-    <cfRule type="expression" dxfId="139" priority="85">
+    <cfRule type="expression" dxfId="67" priority="85">
       <formula>AA$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="87" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="86" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="87" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD18">
+    <cfRule type="cellIs" dxfId="64" priority="60" operator="equal">
       <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="59" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="58">
+      <formula>AD$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE18">
-    <cfRule type="expression" dxfId="136" priority="78">
+    <cfRule type="cellIs" dxfId="61" priority="80" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="78">
       <formula>AE$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="79" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="134" priority="80" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE18:AF25">
+    <cfRule type="cellIs" dxfId="58" priority="27" operator="equal">
       <formula>"P"</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="26" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="25">
+      <formula>AE$3="SUN"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF18:AF25">
-    <cfRule type="expression" dxfId="133" priority="82">
+  <conditionalFormatting sqref="AF18:AG25">
+    <cfRule type="expression" dxfId="55" priority="82">
       <formula>AF$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="83" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="84" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
-    <cfRule type="expression" dxfId="130" priority="67">
-      <formula>I$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="68" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="69" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P18">
-    <cfRule type="expression" dxfId="127" priority="64">
-      <formula>P$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="65" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="66" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W18">
-    <cfRule type="expression" dxfId="124" priority="61">
-      <formula>W$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="62" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="63" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD18">
-    <cfRule type="expression" dxfId="121" priority="58">
-      <formula>AD$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="59" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="60" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F25">
-    <cfRule type="expression" dxfId="115" priority="52">
-      <formula>F$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="53" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="54" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J18:J25">
-    <cfRule type="expression" dxfId="112" priority="49">
-      <formula>J$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="50" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="51" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K18:K25">
-    <cfRule type="expression" dxfId="109" priority="46">
-      <formula>K$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="47" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="48" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L18:L25">
-    <cfRule type="expression" dxfId="106" priority="43">
-      <formula>L$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="44" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="45" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S18:S25">
-    <cfRule type="expression" dxfId="103" priority="40">
-      <formula>S$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="41" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="42" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X18:X25">
-    <cfRule type="expression" dxfId="100" priority="37">
-      <formula>X$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="38" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="39" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y18:Y25">
-    <cfRule type="expression" dxfId="97" priority="34">
-      <formula>Y$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="35" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="36" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z18:Z25">
-    <cfRule type="expression" dxfId="94" priority="31">
-      <formula>Z$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="32" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="33" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE18:AE25">
-    <cfRule type="expression" dxfId="91" priority="28">
-      <formula>AE$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="29" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="30" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF18:AF25">
-    <cfRule type="expression" dxfId="88" priority="25">
-      <formula>AF$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="26" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="27" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D25">
-    <cfRule type="cellIs" dxfId="85" priority="9" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D25">
-    <cfRule type="expression" dxfId="84" priority="10">
-      <formula>D$3="SUN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D25">
-    <cfRule type="cellIs" dxfId="83" priority="11" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="12" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E25">
-    <cfRule type="cellIs" dxfId="81" priority="5" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E25">
-    <cfRule type="expression" dxfId="80" priority="6">
-      <formula>E$3="SUN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E25">
-    <cfRule type="cellIs" dxfId="79" priority="7" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="8" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18:G25">
-    <cfRule type="cellIs" dxfId="77" priority="1" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18:G25">
-    <cfRule type="expression" dxfId="76" priority="2">
-      <formula>G$3="SUN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18:G25">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="84" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10496,41 +9940,41 @@
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="36"/>
     </row>
     <row r="3" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="60" t="str">
+      <c r="A3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="30" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Thu</v>
       </c>
@@ -10597,11 +10041,11 @@
       <c r="T3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="38"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="41"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10610,10 +10054,10 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="31">
         <v>45778</v>
       </c>
       <c r="E4" s="7">
@@ -10690,7 +10134,7 @@
       <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="D5" s="63" t="s">
         <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -10699,7 +10143,7 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -10720,7 +10164,7 @@
       <c r="M5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="40" t="s">
+      <c r="N5" s="42" t="s">
         <v>26</v>
       </c>
       <c r="O5" s="4" t="s">
@@ -10739,15 +10183,15 @@
         <v>6</v>
       </c>
       <c r="T5" s="3">
-        <f>COUNTIF(D5:S5,"P")</f>
+        <f t="shared" ref="T5:T14" si="1">COUNTIF(D5:S5,"P")</f>
         <v>13</v>
       </c>
       <c r="U5" s="4">
-        <f>COUNTIF(D5:S5,"A")</f>
+        <f t="shared" ref="U5:U14" si="2">COUNTIF(D5:S5,"A")</f>
         <v>0</v>
       </c>
       <c r="V5" s="4">
-        <f>COUNTIF(D5:S5,"L")</f>
+        <f t="shared" ref="V5:V14" si="3">COUNTIF(D5:S5,"L")</f>
         <v>0</v>
       </c>
       <c r="W5" s="4">
@@ -10757,7 +10201,7 @@
         <v>5</v>
       </c>
       <c r="Y5" s="16">
-        <f>T5+V5+W5+X5</f>
+        <f t="shared" ref="Y5:Y14" si="4">T5+V5+W5+X5</f>
         <v>20</v>
       </c>
     </row>
@@ -10771,14 +10215,14 @@
       <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="62"/>
+      <c r="D6" s="63"/>
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="40"/>
+      <c r="G6" s="42"/>
       <c r="H6" s="4" t="s">
         <v>6</v>
       </c>
@@ -10797,7 +10241,7 @@
       <c r="M6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="40"/>
+      <c r="N6" s="42"/>
       <c r="O6" s="4" t="s">
         <v>6</v>
       </c>
@@ -10814,15 +10258,15 @@
         <v>6</v>
       </c>
       <c r="T6" s="3">
-        <f>COUNTIF(D6:S6,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="U6" s="4">
-        <f>COUNTIF(D6:S6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V6" s="4">
-        <f>COUNTIF(D6:S6,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W6" s="4">
@@ -10832,7 +10276,7 @@
         <v>5</v>
       </c>
       <c r="Y6" s="16">
-        <f>T6+V6+W6+X6</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -10846,14 +10290,14 @@
       <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="62"/>
+      <c r="D7" s="63"/>
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="40"/>
+      <c r="G7" s="42"/>
       <c r="H7" s="4" t="s">
         <v>6</v>
       </c>
@@ -10872,7 +10316,7 @@
       <c r="M7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="40"/>
+      <c r="N7" s="42"/>
       <c r="O7" s="4" t="s">
         <v>6</v>
       </c>
@@ -10889,15 +10333,15 @@
         <v>6</v>
       </c>
       <c r="T7" s="3">
-        <f>COUNTIF(D7:S7,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="U7" s="4">
-        <f>COUNTIF(D7:S7,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V7" s="4">
-        <f>COUNTIF(D7:S7,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W7" s="4">
@@ -10907,7 +10351,7 @@
         <v>5</v>
       </c>
       <c r="Y7" s="16">
-        <f>T7+V7+W7+X7</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -10921,14 +10365,14 @@
       <c r="C8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="62"/>
+      <c r="D8" s="63"/>
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="40"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="4" t="s">
         <v>6</v>
       </c>
@@ -10947,7 +10391,7 @@
       <c r="M8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N8" s="40"/>
+      <c r="N8" s="42"/>
       <c r="O8" s="4" t="s">
         <v>6</v>
       </c>
@@ -10964,15 +10408,15 @@
         <v>6</v>
       </c>
       <c r="T8" s="3">
-        <f>COUNTIF(D8:S8,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="U8" s="4">
-        <f>COUNTIF(D8:S8,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V8" s="4">
-        <f>COUNTIF(D8:S8,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W8" s="4">
@@ -10982,7 +10426,7 @@
         <v>5</v>
       </c>
       <c r="Y8" s="16">
-        <f>T8+V8+W8+X8</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -10996,14 +10440,14 @@
       <c r="C9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="62"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="40"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="4" t="s">
         <v>6</v>
       </c>
@@ -11022,7 +10466,7 @@
       <c r="M9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N9" s="40"/>
+      <c r="N9" s="42"/>
       <c r="O9" s="4" t="s">
         <v>6</v>
       </c>
@@ -11039,15 +10483,15 @@
         <v>7</v>
       </c>
       <c r="T9" s="3">
-        <f>COUNTIF(D9:S9,"P")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="U9" s="4">
-        <f>COUNTIF(D9:S9,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="V9" s="4">
-        <f>COUNTIF(D9:S9,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="W9" s="4">
@@ -11057,7 +10501,7 @@
         <v>5</v>
       </c>
       <c r="Y9" s="16">
-        <f>T9+V9+W9+X9</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -11071,14 +10515,14 @@
       <c r="C10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="62"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="40"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>6</v>
       </c>
@@ -11097,7 +10541,7 @@
       <c r="M10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="40"/>
+      <c r="N10" s="42"/>
       <c r="O10" s="4" t="s">
         <v>6</v>
       </c>
@@ -11114,15 +10558,15 @@
         <v>6</v>
       </c>
       <c r="T10" s="3">
-        <f>COUNTIF(D10:S10,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="U10" s="4">
-        <f>COUNTIF(D10:S10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V10" s="4">
-        <f>COUNTIF(D10:S10,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W10" s="4">
@@ -11132,7 +10576,7 @@
         <v>5</v>
       </c>
       <c r="Y10" s="16">
-        <f>T10+V10+W10+X10</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -11146,14 +10590,14 @@
       <c r="C11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="62"/>
+      <c r="D11" s="63"/>
       <c r="E11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="40"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="4" t="s">
         <v>6</v>
       </c>
@@ -11172,7 +10616,7 @@
       <c r="M11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N11" s="40"/>
+      <c r="N11" s="42"/>
       <c r="O11" s="4" t="s">
         <v>6</v>
       </c>
@@ -11189,15 +10633,15 @@
         <v>6</v>
       </c>
       <c r="T11" s="3">
-        <f>COUNTIF(D11:S11,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="U11" s="4">
-        <f>COUNTIF(D11:S11,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V11" s="4">
-        <f>COUNTIF(D11:S11,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W11" s="4">
@@ -11207,7 +10651,7 @@
         <v>5</v>
       </c>
       <c r="Y11" s="16">
-        <f>T11+V11+W11+X11</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -11221,14 +10665,14 @@
       <c r="C12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="65"/>
+      <c r="D12" s="64"/>
       <c r="E12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="29"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="4" t="s">
         <v>6</v>
       </c>
@@ -11247,7 +10691,7 @@
       <c r="M12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N12" s="29"/>
+      <c r="N12" s="43"/>
       <c r="O12" s="4" t="s">
         <v>6</v>
       </c>
@@ -11264,15 +10708,15 @@
         <v>6</v>
       </c>
       <c r="T12" s="3">
-        <f>COUNTIF(D12:S12,"P")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="U12" s="4">
-        <f>COUNTIF(D12:S12,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="V12" s="4">
-        <f>COUNTIF(D12:S12,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W12" s="4">
@@ -11282,7 +10726,7 @@
         <v>5</v>
       </c>
       <c r="Y12" s="16">
-        <f>T12+V12+W12+X12</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -11296,14 +10740,14 @@
       <c r="C13" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="65"/>
+      <c r="D13" s="64"/>
       <c r="E13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="29"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="4" t="s">
         <v>6</v>
       </c>
@@ -11322,7 +10766,7 @@
       <c r="M13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="29"/>
+      <c r="N13" s="43"/>
       <c r="O13" s="4" t="s">
         <v>6</v>
       </c>
@@ -11339,15 +10783,15 @@
         <v>6</v>
       </c>
       <c r="T13" s="3">
-        <f>COUNTIF(D13:S13,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="U13" s="4">
-        <f>COUNTIF(D13:S13,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V13" s="4">
-        <f>COUNTIF(D13:S13,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W13" s="4">
@@ -11357,7 +10801,7 @@
         <v>5</v>
       </c>
       <c r="Y13" s="16">
-        <f>T13+V13+W13+X13</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -11371,14 +10815,14 @@
       <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="64"/>
+      <c r="D14" s="65"/>
       <c r="E14" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="41"/>
+      <c r="G14" s="44"/>
       <c r="H14" s="6" t="s">
         <v>6</v>
       </c>
@@ -11397,7 +10841,7 @@
       <c r="M14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="N14" s="41"/>
+      <c r="N14" s="44"/>
       <c r="O14" s="6" t="s">
         <v>6</v>
       </c>
@@ -11414,15 +10858,15 @@
         <v>6</v>
       </c>
       <c r="T14" s="5">
-        <f>COUNTIF(D14:S14,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="U14" s="6">
-        <f>COUNTIF(D14:S14,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V14" s="6">
-        <f>COUNTIF(D14:S14,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W14" s="6">
@@ -11432,118 +10876,118 @@
         <v>5</v>
       </c>
       <c r="Y14" s="17">
-        <f>T14+V14+W14+X14</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="34"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="36"/>
     </row>
     <row r="17" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="60" t="str">
+      <c r="A17" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="38"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="30" t="str">
         <f>TEXT(D18,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="E17" s="15" t="str">
-        <f t="shared" ref="E17:S17" si="1">TEXT(E18,"ddd")</f>
+        <f t="shared" ref="E17:S17" si="5">TEXT(E18,"ddd")</f>
         <v>Fri</v>
       </c>
       <c r="F17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
       <c r="G17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
       <c r="H17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
       <c r="I17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
       <c r="J17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
       <c r="K17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
       <c r="L17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
       <c r="M17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
       <c r="N17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
       <c r="O17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
       <c r="P17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
       <c r="Q17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
       <c r="R17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
       <c r="S17" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
       <c r="T17" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="U17" s="37"/>
-      <c r="V17" s="37"/>
-      <c r="W17" s="37"/>
-      <c r="X17" s="37"/>
-      <c r="Y17" s="38"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="41"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -11552,10 +10996,10 @@
       <c r="B18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="31">
         <v>45778</v>
       </c>
       <c r="E18" s="7">
@@ -11633,7 +11077,7 @@
       <c r="C19" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="62" t="s">
+      <c r="D19" s="63" t="s">
         <v>46</v>
       </c>
       <c r="E19" s="4" t="s">
@@ -11642,7 +11086,7 @@
       <c r="F19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="43" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -11663,7 +11107,7 @@
       <c r="M19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N19" s="29" t="s">
+      <c r="N19" s="43" t="s">
         <v>26</v>
       </c>
       <c r="O19" s="4" t="s">
@@ -11682,15 +11126,15 @@
         <v>6</v>
       </c>
       <c r="T19" s="24">
-        <f>COUNTIF(D19:S19,"P")</f>
+        <f t="shared" ref="T19:T26" si="6">COUNTIF(D19:S19,"P")</f>
         <v>13</v>
       </c>
       <c r="U19" s="8">
-        <f>COUNTIF(D19:S19,"A")</f>
+        <f t="shared" ref="U19:U26" si="7">COUNTIF(D19:S19,"A")</f>
         <v>0</v>
       </c>
       <c r="V19" s="8">
-        <f>COUNTIF(D19:S19,"L")</f>
+        <f t="shared" ref="V19:V26" si="8">COUNTIF(D19:S19,"L")</f>
         <v>0</v>
       </c>
       <c r="W19" s="4">
@@ -11715,14 +11159,14 @@
       <c r="C20" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="62"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="30"/>
+      <c r="G20" s="45"/>
       <c r="H20" s="4" t="s">
         <v>6</v>
       </c>
@@ -11741,7 +11185,7 @@
       <c r="M20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="30"/>
+      <c r="N20" s="45"/>
       <c r="O20" s="4" t="s">
         <v>6</v>
       </c>
@@ -11758,15 +11202,15 @@
         <v>6</v>
       </c>
       <c r="T20" s="24">
-        <f>COUNTIF(D20:S20,"P")</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="U20" s="8">
-        <f>COUNTIF(D20:S20,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V20" s="8">
-        <f>COUNTIF(D20:S20,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W20" s="4">
@@ -11776,13 +11220,13 @@
         <v>5</v>
       </c>
       <c r="Y20" s="16">
-        <f t="shared" ref="Y20:Y26" si="2">T20+V20+W20+X20</f>
+        <f t="shared" ref="Y20:Y26" si="9">T20+V20+W20+X20</f>
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f t="shared" ref="A21:A26" si="3">IF(B21="","",A20+1)</f>
+        <f t="shared" ref="A21:A26" si="10">IF(B21="","",A20+1)</f>
         <v>3</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -11791,14 +11235,14 @@
       <c r="C21" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="62"/>
+      <c r="D21" s="63"/>
       <c r="E21" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="30"/>
+      <c r="G21" s="45"/>
       <c r="H21" s="4" t="s">
         <v>6</v>
       </c>
@@ -11817,7 +11261,7 @@
       <c r="M21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="30"/>
+      <c r="N21" s="45"/>
       <c r="O21" s="4" t="s">
         <v>6</v>
       </c>
@@ -11834,15 +11278,15 @@
         <v>6</v>
       </c>
       <c r="T21" s="24">
-        <f>COUNTIF(D21:S21,"P")</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="U21" s="8">
-        <f>COUNTIF(D21:S21,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V21" s="8">
-        <f>COUNTIF(D21:S21,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W21" s="4">
@@ -11852,13 +11296,13 @@
         <v>5</v>
       </c>
       <c r="Y21" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -11867,14 +11311,14 @@
       <c r="C22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="62"/>
+      <c r="D22" s="63"/>
       <c r="E22" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="30"/>
+      <c r="G22" s="45"/>
       <c r="H22" s="4" t="s">
         <v>6</v>
       </c>
@@ -11893,7 +11337,7 @@
       <c r="M22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N22" s="30"/>
+      <c r="N22" s="45"/>
       <c r="O22" s="4" t="s">
         <v>6</v>
       </c>
@@ -11910,15 +11354,15 @@
         <v>6</v>
       </c>
       <c r="T22" s="24">
-        <f>COUNTIF(D22:S22,"P")</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="U22" s="8">
-        <f>COUNTIF(D22:S22,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V22" s="8">
-        <f>COUNTIF(D22:S22,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W22" s="4">
@@ -11928,13 +11372,13 @@
         <v>5</v>
       </c>
       <c r="Y22" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -11943,14 +11387,14 @@
       <c r="C23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="62"/>
+      <c r="D23" s="63"/>
       <c r="E23" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="30"/>
+      <c r="G23" s="45"/>
       <c r="H23" s="4" t="s">
         <v>6</v>
       </c>
@@ -11969,7 +11413,7 @@
       <c r="M23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N23" s="30"/>
+      <c r="N23" s="45"/>
       <c r="O23" s="4" t="s">
         <v>6</v>
       </c>
@@ -11986,15 +11430,15 @@
         <v>6</v>
       </c>
       <c r="T23" s="24">
-        <f>COUNTIF(D23:S23,"P")</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="U23" s="8">
-        <f>COUNTIF(D23:S23,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V23" s="8">
-        <f>COUNTIF(D23:S23,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W23" s="4">
@@ -12004,13 +11448,13 @@
         <v>5</v>
       </c>
       <c r="Y23" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -12019,14 +11463,14 @@
       <c r="C24" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="63"/>
       <c r="E24" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="30"/>
+      <c r="G24" s="45"/>
       <c r="H24" s="4" t="s">
         <v>6</v>
       </c>
@@ -12045,7 +11489,7 @@
       <c r="M24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N24" s="30"/>
+      <c r="N24" s="45"/>
       <c r="O24" s="4" t="s">
         <v>6</v>
       </c>
@@ -12062,15 +11506,15 @@
         <v>6</v>
       </c>
       <c r="T24" s="24">
-        <f>COUNTIF(D24:S24,"P")</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="U24" s="8">
-        <f>COUNTIF(D24:S24,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V24" s="8">
-        <f>COUNTIF(D24:S24,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W24" s="4">
@@ -12080,13 +11524,13 @@
         <v>5</v>
       </c>
       <c r="Y24" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -12095,14 +11539,14 @@
       <c r="C25" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="62"/>
+      <c r="D25" s="63"/>
       <c r="E25" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="30"/>
+      <c r="G25" s="45"/>
       <c r="H25" s="11" t="s">
         <v>6</v>
       </c>
@@ -12121,7 +11565,7 @@
       <c r="M25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N25" s="30"/>
+      <c r="N25" s="45"/>
       <c r="O25" s="11" t="s">
         <v>6</v>
       </c>
@@ -12134,19 +11578,19 @@
       <c r="R25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S25" s="63" t="s">
+      <c r="S25" s="32" t="s">
         <v>6</v>
       </c>
       <c r="T25" s="25">
-        <f>COUNTIF(D25:S25,"P")</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="U25" s="12">
-        <f>COUNTIF(D25:S25,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V25" s="8">
-        <f>COUNTIF(D25:S25,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W25" s="11">
@@ -12156,13 +11600,13 @@
         <v>5</v>
       </c>
       <c r="Y25" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -12171,14 +11615,14 @@
       <c r="C26" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="64"/>
+      <c r="D26" s="65"/>
       <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="31"/>
+      <c r="G26" s="46"/>
       <c r="H26" s="6" t="s">
         <v>6</v>
       </c>
@@ -12197,7 +11641,7 @@
       <c r="M26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="N26" s="31"/>
+      <c r="N26" s="46"/>
       <c r="O26" s="6" t="s">
         <v>6</v>
       </c>
@@ -12214,15 +11658,15 @@
         <v>6</v>
       </c>
       <c r="T26" s="26">
-        <f>COUNTIF(D26:S26,"P")</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="U26" s="9">
-        <f>COUNTIF(D26:S26,"A")</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V26" s="9">
-        <f>COUNTIF(D26:S26,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W26" s="6">
@@ -12232,12 +11676,17 @@
         <v>5</v>
       </c>
       <c r="Y26" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="T3:Y3"/>
+    <mergeCell ref="G5:G14"/>
+    <mergeCell ref="N5:N14"/>
     <mergeCell ref="G19:G26"/>
     <mergeCell ref="N19:N26"/>
     <mergeCell ref="D5:D14"/>
@@ -12245,284 +11694,203 @@
     <mergeCell ref="A16:Y16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="T17:Y17"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="T3:Y3"/>
-    <mergeCell ref="G5:G14"/>
-    <mergeCell ref="N5:N14"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:S14">
-    <cfRule type="cellIs" dxfId="70" priority="77" operator="equal">
+  <conditionalFormatting sqref="D19:D26">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
       <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:F26">
+    <cfRule type="expression" dxfId="51" priority="2">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:S14">
+    <cfRule type="expression" dxfId="48" priority="6">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:S14">
+    <cfRule type="cellIs" dxfId="47" priority="5" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="7" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="8" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:S18">
+    <cfRule type="expression" dxfId="44" priority="108">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="cellIs" dxfId="43" priority="104" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="103" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="102">
+      <formula>E$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:S26">
-    <cfRule type="cellIs" dxfId="69" priority="73" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="73" operator="equal">
       <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:S4 D17:S18 E5:S14">
-    <cfRule type="expression" dxfId="68" priority="108">
-      <formula>D$3="SUN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:S14">
-    <cfRule type="cellIs" dxfId="67" priority="109" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="110" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="expression" dxfId="65" priority="102">
-      <formula>E$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="103" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="104" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:K26">
-    <cfRule type="expression" dxfId="62" priority="90">
+    <cfRule type="cellIs" dxfId="39" priority="92" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="91" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="90">
       <formula>F$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="91" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="expression" dxfId="36" priority="21">
+      <formula>G$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="22" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="23" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19">
+    <cfRule type="cellIs" dxfId="33" priority="68" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="67" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="66">
+      <formula>I$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19:L26">
+    <cfRule type="expression" dxfId="30" priority="12">
+      <formula>I$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="13" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="14" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="expression" dxfId="59" priority="99">
+    <cfRule type="cellIs" dxfId="27" priority="101" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="100" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="99">
       <formula>L$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="100" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="101" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:R26">
-    <cfRule type="expression" dxfId="56" priority="87">
+    <cfRule type="cellIs" dxfId="24" priority="88" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="89" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="87">
       <formula>M$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="88" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19">
+    <cfRule type="cellIs" dxfId="21" priority="16" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="17" operator="equal">
       <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="15">
+      <formula>N$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19:N26">
+    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="18">
+      <formula>N$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P19">
+    <cfRule type="cellIs" dxfId="15" priority="64" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="63">
+      <formula>P$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="65" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P19:P26">
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="9">
+      <formula>P$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19">
-    <cfRule type="expression" dxfId="53" priority="96">
+    <cfRule type="expression" dxfId="9" priority="96">
       <formula>S$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="97" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="98" operator="equal">
       <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S19:S26">
+    <cfRule type="cellIs" dxfId="6" priority="41" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="40" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="39">
+      <formula>S$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y5:Y14">
-    <cfRule type="cellIs" dxfId="50" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="69" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y5:Y14">
-    <cfRule type="expression" dxfId="49" priority="70">
+    <cfRule type="expression" dxfId="2" priority="70">
       <formula>Y$3="SUN"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y5:Y14">
-    <cfRule type="cellIs" dxfId="48" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="71" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="72" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I19">
-    <cfRule type="expression" dxfId="46" priority="66">
-      <formula>I$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="67" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="68" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P19">
-    <cfRule type="expression" dxfId="43" priority="63">
-      <formula>P$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="64" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="65" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19:E26">
-    <cfRule type="expression" dxfId="40" priority="54">
-      <formula>E$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="55" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="56" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19:F26">
-    <cfRule type="expression" dxfId="37" priority="51">
-      <formula>F$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="52" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="53" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J19:J26">
-    <cfRule type="expression" dxfId="34" priority="48">
-      <formula>J$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="49" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="50" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K19:K26">
-    <cfRule type="expression" dxfId="31" priority="45">
-      <formula>K$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="46" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="47" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L19:L26">
-    <cfRule type="expression" dxfId="28" priority="42">
-      <formula>L$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="43" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="44" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S19:S26">
-    <cfRule type="expression" dxfId="25" priority="39">
-      <formula>S$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="40" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="41" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="expression" dxfId="22" priority="21">
-      <formula>G$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="23" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N19:N26">
-    <cfRule type="expression" dxfId="19" priority="18">
-      <formula>N$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="20" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N19">
-    <cfRule type="expression" dxfId="16" priority="15">
-      <formula>N$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="17" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I19:I26">
-    <cfRule type="expression" dxfId="13" priority="12">
-      <formula>I$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P19:P26">
-    <cfRule type="expression" dxfId="10" priority="9">
-      <formula>P$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D14">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D14">
-    <cfRule type="expression" dxfId="6" priority="6">
-      <formula>D$3="SUN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D14">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19:D26">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"L"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19:D26">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>D$3="SUN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19:D26">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="72" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Sindhi Muslim/Staff Attendance/Staff Attendance - 2nd Year - 3rd QTR.xlsx
+++ b/Sindhi Muslim/Staff Attendance/Staff Attendance - 2nd Year - 3rd QTR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DF5746-25C6-46FB-8336-99EBF8D28A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F61F041-966F-44AF-AE1A-E89ACD411C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY-2025" sheetId="11" r:id="rId1"/>
@@ -720,6 +720,21 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -733,6 +748,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -819,24 +837,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,6 +844,26 @@
   <dxfs count="176">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -854,6 +874,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -864,6 +914,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -874,6 +944,306 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -884,6 +1254,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -894,6 +1284,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -904,6 +1314,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -914,6 +1344,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -944,6 +1404,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -974,6 +1454,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -984,6 +1494,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -994,6 +1524,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1014,6 +1554,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1034,6 +1584,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1074,6 +1644,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1154,6 +1734,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1164,6 +1764,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1174,6 +1784,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1214,6 +1854,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1224,6 +1894,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1244,6 +1924,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1264,6 +1974,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1274,731 +1994,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2892,37 +2892,37 @@
   <sheetData>
     <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="36"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="41"/>
     </row>
     <row r="3" spans="1:21" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="68" t="str">
+      <c r="A3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="34" t="str">
         <f t="shared" ref="D3:O3" si="0">TEXT(D4,"ddd")</f>
         <v>Mon</v>
       </c>
@@ -2970,14 +2970,14 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="P3" s="39" t="s">
+      <c r="P3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="41"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="47"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2989,7 +2989,7 @@
       <c r="C4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="35">
         <v>45705</v>
       </c>
       <c r="E4" s="7">
@@ -3054,13 +3054,13 @@
       <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -3072,7 +3072,7 @@
       <c r="I5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -3123,13 +3123,13 @@
       <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="47"/>
+      <c r="F6" s="53"/>
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3139,7 +3139,7 @@
       <c r="I6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="42"/>
+      <c r="J6" s="48"/>
       <c r="K6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3188,13 +3188,13 @@
       <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="47"/>
+      <c r="F7" s="53"/>
       <c r="G7" s="4" t="s">
         <v>6</v>
       </c>
@@ -3204,7 +3204,7 @@
       <c r="I7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="42"/>
+      <c r="J7" s="48"/>
       <c r="K7" s="4" t="s">
         <v>6</v>
       </c>
@@ -3253,13 +3253,13 @@
       <c r="C8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="47"/>
+      <c r="F8" s="53"/>
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
@@ -3269,7 +3269,7 @@
       <c r="I8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="42"/>
+      <c r="J8" s="48"/>
       <c r="K8" s="4" t="s">
         <v>6</v>
       </c>
@@ -3318,13 +3318,13 @@
       <c r="C9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="47"/>
+      <c r="F9" s="53"/>
       <c r="G9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3334,7 +3334,7 @@
       <c r="I9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="42"/>
+      <c r="J9" s="48"/>
       <c r="K9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3383,13 +3383,13 @@
       <c r="C10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="47"/>
+      <c r="F10" s="53"/>
       <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="I10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="42"/>
+      <c r="J10" s="48"/>
       <c r="K10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3448,13 +3448,13 @@
       <c r="C11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="70" t="s">
+      <c r="D11" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="47"/>
+      <c r="F11" s="53"/>
       <c r="G11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3464,7 +3464,7 @@
       <c r="I11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="42"/>
+      <c r="J11" s="48"/>
       <c r="K11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3513,13 +3513,13 @@
       <c r="C12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="48"/>
+      <c r="F12" s="54"/>
       <c r="G12" s="4" t="s">
         <v>6</v>
       </c>
@@ -3529,7 +3529,7 @@
       <c r="I12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="43"/>
+      <c r="J12" s="49"/>
       <c r="K12" s="4" t="s">
         <v>6</v>
       </c>
@@ -3578,13 +3578,13 @@
       <c r="C13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="D13" s="38" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="49"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="6" t="s">
         <v>24</v>
       </c>
@@ -3594,7 +3594,7 @@
       <c r="I13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="44"/>
+      <c r="J13" s="50"/>
       <c r="K13" s="6" t="s">
         <v>6</v>
       </c>
@@ -3634,37 +3634,37 @@
     </row>
     <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="36"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="41"/>
     </row>
     <row r="16" spans="1:21" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="68" t="str">
+      <c r="A16" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="34" t="str">
         <f t="shared" ref="D16:O16" si="5">TEXT(D17,"ddd")</f>
         <v>Mon</v>
       </c>
@@ -3712,14 +3712,14 @@
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="P16" s="39" t="s">
+      <c r="P16" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="40"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="40"/>
-      <c r="U16" s="41"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="47"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -3731,7 +3731,7 @@
       <c r="C17" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="69">
+      <c r="D17" s="35">
         <v>45705</v>
       </c>
       <c r="E17" s="7">
@@ -3797,13 +3797,13 @@
       <c r="C18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="70" t="s">
+      <c r="D18" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="4" t="s">
@@ -3815,7 +3815,7 @@
       <c r="I18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J18" s="43" t="s">
+      <c r="J18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="K18" s="4" t="s">
@@ -3867,13 +3867,13 @@
       <c r="C19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="D19" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="47"/>
+      <c r="F19" s="53"/>
       <c r="G19" s="4" t="s">
         <v>6</v>
       </c>
@@ -3883,7 +3883,7 @@
       <c r="I19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="45"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="4" t="s">
         <v>6</v>
       </c>
@@ -3933,13 +3933,13 @@
       <c r="C20" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="70" t="s">
+      <c r="D20" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="47"/>
+      <c r="F20" s="53"/>
       <c r="G20" s="4" t="s">
         <v>6</v>
       </c>
@@ -3949,7 +3949,7 @@
       <c r="I20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="45"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="4" t="s">
         <v>6</v>
       </c>
@@ -3999,13 +3999,13 @@
       <c r="C21" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="70" t="s">
+      <c r="D21" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="47"/>
+      <c r="F21" s="53"/>
       <c r="G21" s="4" t="s">
         <v>6</v>
       </c>
@@ -4015,7 +4015,7 @@
       <c r="I21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J21" s="45"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="4" t="s">
         <v>6</v>
       </c>
@@ -4065,13 +4065,13 @@
       <c r="C22" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="70" t="s">
+      <c r="D22" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="47"/>
+      <c r="F22" s="53"/>
       <c r="G22" s="4" t="s">
         <v>6</v>
       </c>
@@ -4081,7 +4081,7 @@
       <c r="I22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J22" s="45"/>
+      <c r="J22" s="51"/>
       <c r="K22" s="4" t="s">
         <v>6</v>
       </c>
@@ -4131,13 +4131,13 @@
       <c r="C23" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="70" t="s">
+      <c r="D23" s="36" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="47"/>
+      <c r="F23" s="53"/>
       <c r="G23" s="4" t="s">
         <v>6</v>
       </c>
@@ -4147,7 +4147,7 @@
       <c r="I23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J23" s="45"/>
+      <c r="J23" s="51"/>
       <c r="K23" s="4" t="s">
         <v>6</v>
       </c>
@@ -4197,13 +4197,13 @@
       <c r="C24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="71" t="s">
+      <c r="D24" s="37" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="47"/>
+      <c r="F24" s="53"/>
       <c r="G24" s="11" t="s">
         <v>6</v>
       </c>
@@ -4213,7 +4213,7 @@
       <c r="I24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J24" s="45"/>
+      <c r="J24" s="51"/>
       <c r="K24" s="11" t="s">
         <v>6</v>
       </c>
@@ -4263,13 +4263,13 @@
       <c r="C25" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="72" t="s">
+      <c r="D25" s="38" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="49"/>
+      <c r="F25" s="55"/>
       <c r="G25" s="6" t="s">
         <v>6</v>
       </c>
@@ -4279,7 +4279,7 @@
       <c r="I25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J25" s="46"/>
+      <c r="J25" s="52"/>
       <c r="K25" s="6" t="s">
         <v>6</v>
       </c>
@@ -4320,6 +4320,9 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="J18:J25"/>
+    <mergeCell ref="F5:F13"/>
+    <mergeCell ref="F18:F25"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="P3:U3"/>
@@ -4327,9 +4330,6 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="P16:U16"/>
     <mergeCell ref="J5:J13"/>
-    <mergeCell ref="J18:J25"/>
-    <mergeCell ref="F5:F13"/>
-    <mergeCell ref="F18:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="D18:E25">
     <cfRule type="expression" dxfId="175" priority="28">
@@ -4424,55 +4424,55 @@
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="36"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="40"/>
+      <c r="AM2" s="40"/>
+      <c r="AN2" s="41"/>
     </row>
     <row r="3" spans="1:40" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
+      <c r="A3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
       <c r="D3" s="15" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Sat</v>
@@ -4597,14 +4597,14 @@
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AI3" s="39" t="s">
+      <c r="AI3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="40"/>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="40"/>
-      <c r="AN3" s="41"/>
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="46"/>
+      <c r="AL3" s="46"/>
+      <c r="AM3" s="46"/>
+      <c r="AN3" s="47"/>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -4741,7 +4741,7 @@
       <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -4762,7 +4762,7 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="42" t="s">
+      <c r="L5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="M5" s="4" t="s">
@@ -4783,7 +4783,7 @@
       <c r="R5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="S5" s="42" t="s">
+      <c r="S5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="T5" s="4" t="s">
@@ -4804,7 +4804,7 @@
       <c r="Y5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="42" t="s">
+      <c r="Z5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="AA5" s="4" t="s">
@@ -4819,16 +4819,16 @@
       <c r="AD5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE5" s="50" t="s">
+      <c r="AE5" s="56" t="s">
         <v>43</v>
       </c>
       <c r="AF5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG5" s="42" t="s">
+      <c r="AG5" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="AH5" s="58" t="s">
+      <c r="AH5" s="64" t="s">
         <v>44</v>
       </c>
       <c r="AI5" s="3">
@@ -4867,7 +4867,7 @@
       <c r="D6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="42"/>
+      <c r="E6" s="48"/>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4886,7 +4886,7 @@
       <c r="K6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="42"/>
+      <c r="L6" s="48"/>
       <c r="M6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4905,7 +4905,7 @@
       <c r="R6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S6" s="42"/>
+      <c r="S6" s="48"/>
       <c r="T6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4924,7 +4924,7 @@
       <c r="Y6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z6" s="42"/>
+      <c r="Z6" s="48"/>
       <c r="AA6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4937,12 +4937,12 @@
       <c r="AD6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE6" s="50"/>
+      <c r="AE6" s="56"/>
       <c r="AF6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG6" s="42"/>
-      <c r="AH6" s="58"/>
+      <c r="AG6" s="48"/>
+      <c r="AH6" s="64"/>
       <c r="AI6" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -4979,7 +4979,7 @@
       <c r="D7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="42"/>
+      <c r="E7" s="48"/>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4998,7 +4998,7 @@
       <c r="K7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="42"/>
+      <c r="L7" s="48"/>
       <c r="M7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5017,7 +5017,7 @@
       <c r="R7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S7" s="42"/>
+      <c r="S7" s="48"/>
       <c r="T7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5036,7 +5036,7 @@
       <c r="Y7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z7" s="42"/>
+      <c r="Z7" s="48"/>
       <c r="AA7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5049,12 +5049,12 @@
       <c r="AD7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE7" s="50"/>
+      <c r="AE7" s="56"/>
       <c r="AF7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="42"/>
-      <c r="AH7" s="58"/>
+      <c r="AG7" s="48"/>
+      <c r="AH7" s="64"/>
       <c r="AI7" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -5091,7 +5091,7 @@
       <c r="D8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="42"/>
+      <c r="E8" s="48"/>
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5110,7 +5110,7 @@
       <c r="K8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="42"/>
+      <c r="L8" s="48"/>
       <c r="M8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5129,7 +5129,7 @@
       <c r="R8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S8" s="42"/>
+      <c r="S8" s="48"/>
       <c r="T8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5148,7 +5148,7 @@
       <c r="Y8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z8" s="42"/>
+      <c r="Z8" s="48"/>
       <c r="AA8" s="4" t="s">
         <v>6</v>
       </c>
@@ -5161,12 +5161,12 @@
       <c r="AD8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE8" s="50"/>
+      <c r="AE8" s="56"/>
       <c r="AF8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG8" s="42"/>
-      <c r="AH8" s="58"/>
+      <c r="AG8" s="48"/>
+      <c r="AH8" s="64"/>
       <c r="AI8" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -5203,7 +5203,7 @@
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="42"/>
+      <c r="E9" s="48"/>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5222,7 +5222,7 @@
       <c r="K9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L9" s="42"/>
+      <c r="L9" s="48"/>
       <c r="M9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5241,7 +5241,7 @@
       <c r="R9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S9" s="42"/>
+      <c r="S9" s="48"/>
       <c r="T9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="Y9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z9" s="42"/>
+      <c r="Z9" s="48"/>
       <c r="AA9" s="4" t="s">
         <v>6</v>
       </c>
@@ -5273,12 +5273,12 @@
       <c r="AD9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE9" s="50"/>
+      <c r="AE9" s="56"/>
       <c r="AF9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG9" s="42"/>
-      <c r="AH9" s="58"/>
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="64"/>
       <c r="AI9" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -5315,7 +5315,7 @@
       <c r="D10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="42"/>
+      <c r="E10" s="48"/>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5334,7 +5334,7 @@
       <c r="K10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="42"/>
+      <c r="L10" s="48"/>
       <c r="M10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5353,7 +5353,7 @@
       <c r="R10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S10" s="42"/>
+      <c r="S10" s="48"/>
       <c r="T10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5372,7 +5372,7 @@
       <c r="Y10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z10" s="42"/>
+      <c r="Z10" s="48"/>
       <c r="AA10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5385,12 +5385,12 @@
       <c r="AD10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE10" s="50"/>
+      <c r="AE10" s="56"/>
       <c r="AF10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG10" s="42"/>
-      <c r="AH10" s="58"/>
+      <c r="AG10" s="48"/>
+      <c r="AH10" s="64"/>
       <c r="AI10" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -5427,7 +5427,7 @@
       <c r="D11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="42"/>
+      <c r="E11" s="48"/>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="K11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="42"/>
+      <c r="L11" s="48"/>
       <c r="M11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5465,7 +5465,7 @@
       <c r="R11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="42"/>
+      <c r="S11" s="48"/>
       <c r="T11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5484,7 +5484,7 @@
       <c r="Y11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z11" s="42"/>
+      <c r="Z11" s="48"/>
       <c r="AA11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5497,12 +5497,12 @@
       <c r="AD11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE11" s="50"/>
+      <c r="AE11" s="56"/>
       <c r="AF11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG11" s="42"/>
-      <c r="AH11" s="58"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="64"/>
       <c r="AI11" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -5539,7 +5539,7 @@
       <c r="D12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="43"/>
+      <c r="E12" s="49"/>
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
@@ -5558,7 +5558,7 @@
       <c r="K12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="43"/>
+      <c r="L12" s="49"/>
       <c r="M12" s="4" t="s">
         <v>24</v>
       </c>
@@ -5577,7 +5577,7 @@
       <c r="R12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="S12" s="43"/>
+      <c r="S12" s="49"/>
       <c r="T12" s="4" t="s">
         <v>24</v>
       </c>
@@ -5596,7 +5596,7 @@
       <c r="Y12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z12" s="43"/>
+      <c r="Z12" s="49"/>
       <c r="AA12" s="4" t="s">
         <v>24</v>
       </c>
@@ -5609,12 +5609,12 @@
       <c r="AD12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AE12" s="51"/>
+      <c r="AE12" s="57"/>
       <c r="AF12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AG12" s="43"/>
-      <c r="AH12" s="55"/>
+      <c r="AG12" s="49"/>
+      <c r="AH12" s="61"/>
       <c r="AI12" s="3">
         <f t="shared" ref="AI12" si="5">COUNTIF(D12:AH12,"P")</f>
         <v>2</v>
@@ -5650,7 +5650,7 @@
       <c r="D13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="44"/>
+      <c r="E13" s="50"/>
       <c r="F13" s="6" t="s">
         <v>6</v>
       </c>
@@ -5669,7 +5669,7 @@
       <c r="K13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L13" s="44"/>
+      <c r="L13" s="50"/>
       <c r="M13" s="6" t="s">
         <v>6</v>
       </c>
@@ -5688,7 +5688,7 @@
       <c r="R13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S13" s="44"/>
+      <c r="S13" s="50"/>
       <c r="T13" s="6" t="s">
         <v>6</v>
       </c>
@@ -5707,7 +5707,7 @@
       <c r="Y13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Z13" s="44"/>
+      <c r="Z13" s="50"/>
       <c r="AA13" s="6" t="s">
         <v>6</v>
       </c>
@@ -5720,12 +5720,12 @@
       <c r="AD13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AE13" s="52"/>
+      <c r="AE13" s="58"/>
       <c r="AF13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AG13" s="44"/>
-      <c r="AH13" s="59"/>
+      <c r="AG13" s="50"/>
+      <c r="AH13" s="65"/>
       <c r="AI13" s="5">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -5751,55 +5751,55 @@
     </row>
     <row r="14" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="35"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="35"/>
-      <c r="AE15" s="35"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="35"/>
-      <c r="AJ15" s="35"/>
-      <c r="AK15" s="35"/>
-      <c r="AL15" s="35"/>
-      <c r="AM15" s="35"/>
-      <c r="AN15" s="36"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="40"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="40"/>
+      <c r="AM15" s="40"/>
+      <c r="AN15" s="41"/>
     </row>
     <row r="16" spans="1:40" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
+      <c r="A16" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="15" t="str">
         <f>TEXT(D17,"ddd")</f>
         <v>Sat</v>
@@ -5924,14 +5924,14 @@
         <f t="shared" si="8"/>
         <v>Mon</v>
       </c>
-      <c r="AI16" s="39" t="s">
+      <c r="AI16" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="AJ16" s="40"/>
-      <c r="AK16" s="40"/>
-      <c r="AL16" s="40"/>
-      <c r="AM16" s="40"/>
-      <c r="AN16" s="41"/>
+      <c r="AJ16" s="46"/>
+      <c r="AK16" s="46"/>
+      <c r="AL16" s="46"/>
+      <c r="AM16" s="46"/>
+      <c r="AN16" s="47"/>
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -6069,7 +6069,7 @@
       <c r="D18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -6090,7 +6090,7 @@
       <c r="K18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L18" s="43" t="s">
+      <c r="L18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="M18" s="4" t="s">
@@ -6111,7 +6111,7 @@
       <c r="R18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S18" s="43" t="s">
+      <c r="S18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="T18" s="4" t="s">
@@ -6132,7 +6132,7 @@
       <c r="Y18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z18" s="43" t="s">
+      <c r="Z18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="AA18" s="4" t="s">
@@ -6147,16 +6147,16 @@
       <c r="AD18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE18" s="51" t="s">
+      <c r="AE18" s="57" t="s">
         <v>43</v>
       </c>
       <c r="AF18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG18" s="43" t="s">
+      <c r="AG18" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="AH18" s="55" t="s">
+      <c r="AH18" s="61" t="s">
         <v>44</v>
       </c>
       <c r="AI18" s="24">
@@ -6196,7 +6196,7 @@
       <c r="D19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="45"/>
+      <c r="E19" s="51"/>
       <c r="F19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6215,7 +6215,7 @@
       <c r="K19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L19" s="45"/>
+      <c r="L19" s="51"/>
       <c r="M19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6234,7 +6234,7 @@
       <c r="R19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S19" s="45"/>
+      <c r="S19" s="51"/>
       <c r="T19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6253,7 +6253,7 @@
       <c r="Y19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z19" s="45"/>
+      <c r="Z19" s="51"/>
       <c r="AA19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6266,12 +6266,12 @@
       <c r="AD19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE19" s="53"/>
+      <c r="AE19" s="59"/>
       <c r="AF19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG19" s="45"/>
-      <c r="AH19" s="56"/>
+      <c r="AG19" s="51"/>
+      <c r="AH19" s="62"/>
       <c r="AI19" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6309,7 +6309,7 @@
       <c r="D20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="45"/>
+      <c r="E20" s="51"/>
       <c r="F20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6328,7 +6328,7 @@
       <c r="K20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L20" s="45"/>
+      <c r="L20" s="51"/>
       <c r="M20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6347,7 +6347,7 @@
       <c r="R20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S20" s="45"/>
+      <c r="S20" s="51"/>
       <c r="T20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6366,7 +6366,7 @@
       <c r="Y20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z20" s="45"/>
+      <c r="Z20" s="51"/>
       <c r="AA20" s="4" t="s">
         <v>6</v>
       </c>
@@ -6379,12 +6379,12 @@
       <c r="AD20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE20" s="53"/>
+      <c r="AE20" s="59"/>
       <c r="AF20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG20" s="45"/>
-      <c r="AH20" s="56"/>
+      <c r="AG20" s="51"/>
+      <c r="AH20" s="62"/>
       <c r="AI20" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6422,7 +6422,7 @@
       <c r="D21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="45"/>
+      <c r="E21" s="51"/>
       <c r="F21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6441,7 +6441,7 @@
       <c r="K21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="45"/>
+      <c r="L21" s="51"/>
       <c r="M21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6460,7 +6460,7 @@
       <c r="R21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S21" s="45"/>
+      <c r="S21" s="51"/>
       <c r="T21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6479,7 +6479,7 @@
       <c r="Y21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z21" s="45"/>
+      <c r="Z21" s="51"/>
       <c r="AA21" s="4" t="s">
         <v>6</v>
       </c>
@@ -6492,12 +6492,12 @@
       <c r="AD21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE21" s="53"/>
+      <c r="AE21" s="59"/>
       <c r="AF21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG21" s="45"/>
-      <c r="AH21" s="56"/>
+      <c r="AG21" s="51"/>
+      <c r="AH21" s="62"/>
       <c r="AI21" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6535,7 +6535,7 @@
       <c r="D22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="45"/>
+      <c r="E22" s="51"/>
       <c r="F22" s="4" t="s">
         <v>6</v>
       </c>
@@ -6554,7 +6554,7 @@
       <c r="K22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="45"/>
+      <c r="L22" s="51"/>
       <c r="M22" s="4" t="s">
         <v>6</v>
       </c>
@@ -6573,7 +6573,7 @@
       <c r="R22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S22" s="45"/>
+      <c r="S22" s="51"/>
       <c r="T22" s="4" t="s">
         <v>6</v>
       </c>
@@ -6592,7 +6592,7 @@
       <c r="Y22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z22" s="45"/>
+      <c r="Z22" s="51"/>
       <c r="AA22" s="4" t="s">
         <v>6</v>
       </c>
@@ -6605,12 +6605,12 @@
       <c r="AD22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE22" s="53"/>
+      <c r="AE22" s="59"/>
       <c r="AF22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG22" s="45"/>
-      <c r="AH22" s="56"/>
+      <c r="AG22" s="51"/>
+      <c r="AH22" s="62"/>
       <c r="AI22" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6648,7 +6648,7 @@
       <c r="D23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="45"/>
+      <c r="E23" s="51"/>
       <c r="F23" s="4" t="s">
         <v>6</v>
       </c>
@@ -6667,7 +6667,7 @@
       <c r="K23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L23" s="45"/>
+      <c r="L23" s="51"/>
       <c r="M23" s="4" t="s">
         <v>6</v>
       </c>
@@ -6686,7 +6686,7 @@
       <c r="R23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S23" s="45"/>
+      <c r="S23" s="51"/>
       <c r="T23" s="4" t="s">
         <v>6</v>
       </c>
@@ -6705,7 +6705,7 @@
       <c r="Y23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z23" s="45"/>
+      <c r="Z23" s="51"/>
       <c r="AA23" s="4" t="s">
         <v>6</v>
       </c>
@@ -6718,12 +6718,12 @@
       <c r="AD23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE23" s="53"/>
+      <c r="AE23" s="59"/>
       <c r="AF23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG23" s="45"/>
-      <c r="AH23" s="56"/>
+      <c r="AG23" s="51"/>
+      <c r="AH23" s="62"/>
       <c r="AI23" s="24">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6761,7 +6761,7 @@
       <c r="D24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="45"/>
+      <c r="E24" s="51"/>
       <c r="F24" s="11" t="s">
         <v>6</v>
       </c>
@@ -6780,7 +6780,7 @@
       <c r="K24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L24" s="45"/>
+      <c r="L24" s="51"/>
       <c r="M24" s="11" t="s">
         <v>6</v>
       </c>
@@ -6799,7 +6799,7 @@
       <c r="R24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S24" s="45"/>
+      <c r="S24" s="51"/>
       <c r="T24" s="11" t="s">
         <v>6</v>
       </c>
@@ -6818,7 +6818,7 @@
       <c r="Y24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="Z24" s="45"/>
+      <c r="Z24" s="51"/>
       <c r="AA24" s="11" t="s">
         <v>6</v>
       </c>
@@ -6831,12 +6831,12 @@
       <c r="AD24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AE24" s="53"/>
+      <c r="AE24" s="59"/>
       <c r="AF24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AG24" s="45"/>
-      <c r="AH24" s="56"/>
+      <c r="AG24" s="51"/>
+      <c r="AH24" s="62"/>
       <c r="AI24" s="25">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -6874,7 +6874,7 @@
       <c r="D25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="46"/>
+      <c r="E25" s="52"/>
       <c r="F25" s="6" t="s">
         <v>6</v>
       </c>
@@ -6893,7 +6893,7 @@
       <c r="K25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L25" s="46"/>
+      <c r="L25" s="52"/>
       <c r="M25" s="6" t="s">
         <v>6</v>
       </c>
@@ -6912,7 +6912,7 @@
       <c r="R25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S25" s="46"/>
+      <c r="S25" s="52"/>
       <c r="T25" s="6" t="s">
         <v>6</v>
       </c>
@@ -6931,7 +6931,7 @@
       <c r="Y25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Z25" s="46"/>
+      <c r="Z25" s="52"/>
       <c r="AA25" s="6" t="s">
         <v>6</v>
       </c>
@@ -6944,12 +6944,12 @@
       <c r="AD25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AE25" s="54"/>
+      <c r="AE25" s="60"/>
       <c r="AF25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AG25" s="46"/>
-      <c r="AH25" s="57"/>
+      <c r="AG25" s="52"/>
+      <c r="AH25" s="63"/>
       <c r="AI25" s="26">
         <f t="shared" si="9"/>
         <v>23</v>
@@ -6975,6 +6975,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A2:AN2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="E5:E13"/>
+    <mergeCell ref="L5:L13"/>
+    <mergeCell ref="S5:S13"/>
+    <mergeCell ref="Z5:Z13"/>
     <mergeCell ref="AG18:AG25"/>
     <mergeCell ref="AG5:AG13"/>
     <mergeCell ref="AE5:AE13"/>
@@ -6988,13 +6995,6 @@
     <mergeCell ref="L18:L25"/>
     <mergeCell ref="S18:S25"/>
     <mergeCell ref="Z18:Z25"/>
-    <mergeCell ref="A2:AN2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="AI3:AN3"/>
-    <mergeCell ref="E5:E13"/>
-    <mergeCell ref="L5:L13"/>
-    <mergeCell ref="S5:S13"/>
-    <mergeCell ref="Z5:Z13"/>
   </mergeCells>
   <conditionalFormatting sqref="D18:D25">
     <cfRule type="expression" dxfId="157" priority="123">
@@ -7176,54 +7176,54 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="36"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="40"/>
+      <c r="AM2" s="41"/>
     </row>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
+      <c r="A3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
       <c r="D3" s="15" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
@@ -7344,14 +7344,14 @@
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AH3" s="39" t="s">
+      <c r="AH3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="AI3" s="40"/>
-      <c r="AJ3" s="40"/>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="41"/>
+      <c r="AI3" s="46"/>
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="46"/>
+      <c r="AL3" s="46"/>
+      <c r="AM3" s="47"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -7482,22 +7482,22 @@
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E5" s="64" t="s">
         <v>44</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="60" t="s">
+      <c r="G5" s="66" t="s">
         <v>45</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="4" t="s">
@@ -7518,7 +7518,7 @@
       <c r="O5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="42" t="s">
+      <c r="P5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="Q5" s="4" t="s">
@@ -7539,7 +7539,7 @@
       <c r="V5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W5" s="42" t="s">
+      <c r="W5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="X5" s="4" t="s">
@@ -7560,7 +7560,7 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="42" t="s">
+      <c r="AD5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="AE5" s="4" t="s">
@@ -7605,16 +7605,16 @@
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="60"/>
+      <c r="G6" s="66"/>
       <c r="H6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="42"/>
+      <c r="I6" s="48"/>
       <c r="J6" s="4" t="s">
         <v>6</v>
       </c>
@@ -7633,7 +7633,7 @@
       <c r="O6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="42"/>
+      <c r="P6" s="48"/>
       <c r="Q6" s="4" t="s">
         <v>6</v>
       </c>
@@ -7652,7 +7652,7 @@
       <c r="V6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="42"/>
+      <c r="W6" s="48"/>
       <c r="X6" s="4" t="s">
         <v>6</v>
       </c>
@@ -7671,7 +7671,7 @@
       <c r="AC6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD6" s="42"/>
+      <c r="AD6" s="48"/>
       <c r="AE6" s="4" t="s">
         <v>6</v>
       </c>
@@ -7714,16 +7714,16 @@
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="60"/>
+      <c r="G7" s="66"/>
       <c r="H7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="42"/>
+      <c r="I7" s="48"/>
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
@@ -7742,7 +7742,7 @@
       <c r="O7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P7" s="42"/>
+      <c r="P7" s="48"/>
       <c r="Q7" s="4" t="s">
         <v>6</v>
       </c>
@@ -7761,7 +7761,7 @@
       <c r="V7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="42"/>
+      <c r="W7" s="48"/>
       <c r="X7" s="4" t="s">
         <v>6</v>
       </c>
@@ -7780,7 +7780,7 @@
       <c r="AC7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD7" s="42"/>
+      <c r="AD7" s="48"/>
       <c r="AE7" s="4" t="s">
         <v>6</v>
       </c>
@@ -7823,16 +7823,16 @@
       <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
       <c r="F8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="60"/>
+      <c r="G8" s="66"/>
       <c r="H8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="42"/>
+      <c r="I8" s="48"/>
       <c r="J8" s="4" t="s">
         <v>6</v>
       </c>
@@ -7851,7 +7851,7 @@
       <c r="O8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P8" s="42"/>
+      <c r="P8" s="48"/>
       <c r="Q8" s="4" t="s">
         <v>6</v>
       </c>
@@ -7870,7 +7870,7 @@
       <c r="V8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W8" s="42"/>
+      <c r="W8" s="48"/>
       <c r="X8" s="4" t="s">
         <v>6</v>
       </c>
@@ -7889,7 +7889,7 @@
       <c r="AC8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD8" s="42"/>
+      <c r="AD8" s="48"/>
       <c r="AE8" s="4" t="s">
         <v>6</v>
       </c>
@@ -7932,16 +7932,16 @@
       <c r="C9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="60"/>
+      <c r="G9" s="66"/>
       <c r="H9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="42"/>
+      <c r="I9" s="48"/>
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
@@ -7960,7 +7960,7 @@
       <c r="O9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P9" s="42"/>
+      <c r="P9" s="48"/>
       <c r="Q9" s="4" t="s">
         <v>6</v>
       </c>
@@ -7979,7 +7979,7 @@
       <c r="V9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W9" s="42"/>
+      <c r="W9" s="48"/>
       <c r="X9" s="4" t="s">
         <v>6</v>
       </c>
@@ -7998,7 +7998,7 @@
       <c r="AC9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="42"/>
+      <c r="AD9" s="48"/>
       <c r="AE9" s="4" t="s">
         <v>6</v>
       </c>
@@ -8041,16 +8041,16 @@
       <c r="C10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="60"/>
+      <c r="G10" s="66"/>
       <c r="H10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="42"/>
+      <c r="I10" s="48"/>
       <c r="J10" s="4" t="s">
         <v>6</v>
       </c>
@@ -8069,7 +8069,7 @@
       <c r="O10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="42"/>
+      <c r="P10" s="48"/>
       <c r="Q10" s="4" t="s">
         <v>6</v>
       </c>
@@ -8088,7 +8088,7 @@
       <c r="V10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W10" s="42"/>
+      <c r="W10" s="48"/>
       <c r="X10" s="4" t="s">
         <v>6</v>
       </c>
@@ -8107,7 +8107,7 @@
       <c r="AC10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD10" s="42"/>
+      <c r="AD10" s="48"/>
       <c r="AE10" s="4" t="s">
         <v>6</v>
       </c>
@@ -8150,16 +8150,16 @@
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="60"/>
+      <c r="G11" s="66"/>
       <c r="H11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="42"/>
+      <c r="I11" s="48"/>
       <c r="J11" s="4" t="s">
         <v>6</v>
       </c>
@@ -8178,7 +8178,7 @@
       <c r="O11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P11" s="42"/>
+      <c r="P11" s="48"/>
       <c r="Q11" s="4" t="s">
         <v>6</v>
       </c>
@@ -8197,7 +8197,7 @@
       <c r="V11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W11" s="42"/>
+      <c r="W11" s="48"/>
       <c r="X11" s="4" t="s">
         <v>6</v>
       </c>
@@ -8216,7 +8216,7 @@
       <c r="AC11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD11" s="42"/>
+      <c r="AD11" s="48"/>
       <c r="AE11" s="4" t="s">
         <v>6</v>
       </c>
@@ -8259,16 +8259,16 @@
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="61"/>
+      <c r="G12" s="67"/>
       <c r="H12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="43"/>
+      <c r="I12" s="49"/>
       <c r="J12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8287,7 +8287,7 @@
       <c r="O12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="P12" s="43"/>
+      <c r="P12" s="49"/>
       <c r="Q12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8306,7 +8306,7 @@
       <c r="V12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W12" s="43"/>
+      <c r="W12" s="49"/>
       <c r="X12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8325,7 +8325,7 @@
       <c r="AC12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="AD12" s="43"/>
+      <c r="AD12" s="49"/>
       <c r="AE12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8368,16 +8368,16 @@
       <c r="C13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
       <c r="F13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="62"/>
+      <c r="G13" s="68"/>
       <c r="H13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="44"/>
+      <c r="I13" s="50"/>
       <c r="J13" s="6" t="s">
         <v>24</v>
       </c>
@@ -8396,7 +8396,7 @@
       <c r="O13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="P13" s="44"/>
+      <c r="P13" s="50"/>
       <c r="Q13" s="6" t="s">
         <v>24</v>
       </c>
@@ -8415,7 +8415,7 @@
       <c r="V13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="W13" s="44"/>
+      <c r="W13" s="50"/>
       <c r="X13" s="6" t="s">
         <v>24</v>
       </c>
@@ -8434,7 +8434,7 @@
       <c r="AC13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AD13" s="44"/>
+      <c r="AD13" s="50"/>
       <c r="AE13" s="6" t="s">
         <v>6</v>
       </c>
@@ -8468,54 +8468,54 @@
     </row>
     <row r="14" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="35"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="35"/>
-      <c r="AE15" s="35"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="35"/>
-      <c r="AJ15" s="35"/>
-      <c r="AK15" s="35"/>
-      <c r="AL15" s="35"/>
-      <c r="AM15" s="36"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="40"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="40"/>
+      <c r="AM15" s="41"/>
     </row>
     <row r="16" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
+      <c r="A16" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="15" t="str">
         <f>TEXT(D17,"ddd")</f>
         <v>Tue</v>
@@ -8636,14 +8636,14 @@
         <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="AH16" s="39" t="s">
+      <c r="AH16" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="AI16" s="40"/>
-      <c r="AJ16" s="40"/>
-      <c r="AK16" s="40"/>
-      <c r="AL16" s="40"/>
-      <c r="AM16" s="41"/>
+      <c r="AI16" s="46"/>
+      <c r="AJ16" s="46"/>
+      <c r="AK16" s="46"/>
+      <c r="AL16" s="46"/>
+      <c r="AM16" s="47"/>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -8775,22 +8775,22 @@
       <c r="C18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="64" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="60" t="s">
+      <c r="G18" s="66" t="s">
         <v>45</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="43" t="s">
+      <c r="I18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -8811,7 +8811,7 @@
       <c r="O18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P18" s="43" t="s">
+      <c r="P18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="Q18" s="4" t="s">
@@ -8832,7 +8832,7 @@
       <c r="V18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W18" s="43" t="s">
+      <c r="W18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="X18" s="4" t="s">
@@ -8853,7 +8853,7 @@
       <c r="AC18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD18" s="43" t="s">
+      <c r="AD18" s="49" t="s">
         <v>26</v>
       </c>
       <c r="AE18" s="4" t="s">
@@ -8899,16 +8899,16 @@
       <c r="C19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
       <c r="F19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="60"/>
+      <c r="G19" s="66"/>
       <c r="H19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I19" s="45"/>
+      <c r="I19" s="51"/>
       <c r="J19" s="4" t="s">
         <v>6</v>
       </c>
@@ -8927,7 +8927,7 @@
       <c r="O19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P19" s="45"/>
+      <c r="P19" s="51"/>
       <c r="Q19" s="4" t="s">
         <v>6</v>
       </c>
@@ -8946,7 +8946,7 @@
       <c r="V19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W19" s="45"/>
+      <c r="W19" s="51"/>
       <c r="X19" s="4" t="s">
         <v>6</v>
       </c>
@@ -8965,7 +8965,7 @@
       <c r="AC19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD19" s="45"/>
+      <c r="AD19" s="51"/>
       <c r="AE19" s="4" t="s">
         <v>6</v>
       </c>
@@ -9009,16 +9009,16 @@
       <c r="C20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
       <c r="F20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="60"/>
+      <c r="G20" s="66"/>
       <c r="H20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="45"/>
+      <c r="I20" s="51"/>
       <c r="J20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9037,7 +9037,7 @@
       <c r="O20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P20" s="45"/>
+      <c r="P20" s="51"/>
       <c r="Q20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9056,7 +9056,7 @@
       <c r="V20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W20" s="45"/>
+      <c r="W20" s="51"/>
       <c r="X20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9075,7 +9075,7 @@
       <c r="AC20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD20" s="45"/>
+      <c r="AD20" s="51"/>
       <c r="AE20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9119,16 +9119,16 @@
       <c r="C21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
       <c r="F21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="60"/>
+      <c r="G21" s="66"/>
       <c r="H21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="45"/>
+      <c r="I21" s="51"/>
       <c r="J21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9147,7 +9147,7 @@
       <c r="O21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P21" s="45"/>
+      <c r="P21" s="51"/>
       <c r="Q21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9166,7 +9166,7 @@
       <c r="V21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W21" s="45"/>
+      <c r="W21" s="51"/>
       <c r="X21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9185,7 +9185,7 @@
       <c r="AC21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD21" s="45"/>
+      <c r="AD21" s="51"/>
       <c r="AE21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9229,16 +9229,16 @@
       <c r="C22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
       <c r="F22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="60"/>
+      <c r="G22" s="66"/>
       <c r="H22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="45"/>
+      <c r="I22" s="51"/>
       <c r="J22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9257,7 +9257,7 @@
       <c r="O22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P22" s="45"/>
+      <c r="P22" s="51"/>
       <c r="Q22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9276,7 +9276,7 @@
       <c r="V22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W22" s="45"/>
+      <c r="W22" s="51"/>
       <c r="X22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9295,7 +9295,7 @@
       <c r="AC22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD22" s="45"/>
+      <c r="AD22" s="51"/>
       <c r="AE22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9339,16 +9339,16 @@
       <c r="C23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
       <c r="F23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="60"/>
+      <c r="G23" s="66"/>
       <c r="H23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="45"/>
+      <c r="I23" s="51"/>
       <c r="J23" s="4" t="s">
         <v>6</v>
       </c>
@@ -9367,7 +9367,7 @@
       <c r="O23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P23" s="45"/>
+      <c r="P23" s="51"/>
       <c r="Q23" s="4" t="s">
         <v>6</v>
       </c>
@@ -9386,7 +9386,7 @@
       <c r="V23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W23" s="45"/>
+      <c r="W23" s="51"/>
       <c r="X23" s="4" t="s">
         <v>6</v>
       </c>
@@ -9405,7 +9405,7 @@
       <c r="AC23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AD23" s="45"/>
+      <c r="AD23" s="51"/>
       <c r="AE23" s="4" t="s">
         <v>6</v>
       </c>
@@ -9449,16 +9449,16 @@
       <c r="C24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
       <c r="F24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="60"/>
+      <c r="G24" s="66"/>
       <c r="H24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="45"/>
+      <c r="I24" s="51"/>
       <c r="J24" s="11" t="s">
         <v>6</v>
       </c>
@@ -9477,7 +9477,7 @@
       <c r="O24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P24" s="45"/>
+      <c r="P24" s="51"/>
       <c r="Q24" s="11" t="s">
         <v>6</v>
       </c>
@@ -9496,7 +9496,7 @@
       <c r="V24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="W24" s="45"/>
+      <c r="W24" s="51"/>
       <c r="X24" s="11" t="s">
         <v>6</v>
       </c>
@@ -9515,7 +9515,7 @@
       <c r="AC24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AD24" s="45"/>
+      <c r="AD24" s="51"/>
       <c r="AE24" s="11" t="s">
         <v>6</v>
       </c>
@@ -9559,16 +9559,16 @@
       <c r="C25" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
       <c r="F25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="62"/>
+      <c r="G25" s="68"/>
       <c r="H25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I25" s="46"/>
+      <c r="I25" s="52"/>
       <c r="J25" s="6" t="s">
         <v>6</v>
       </c>
@@ -9587,7 +9587,7 @@
       <c r="O25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="P25" s="46"/>
+      <c r="P25" s="52"/>
       <c r="Q25" s="6" t="s">
         <v>6</v>
       </c>
@@ -9606,7 +9606,7 @@
       <c r="V25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="W25" s="46"/>
+      <c r="W25" s="52"/>
       <c r="X25" s="6" t="s">
         <v>6</v>
       </c>
@@ -9625,7 +9625,7 @@
       <c r="AC25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AD25" s="46"/>
+      <c r="AD25" s="52"/>
       <c r="AE25" s="6" t="s">
         <v>6</v>
       </c>
@@ -9660,6 +9660,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="I18:I25"/>
+    <mergeCell ref="P18:P25"/>
+    <mergeCell ref="W18:W25"/>
+    <mergeCell ref="AD18:AD25"/>
+    <mergeCell ref="A15:AM15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="AH16:AM16"/>
+    <mergeCell ref="D18:D25"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="G18:G25"/>
     <mergeCell ref="A2:AM2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="AH3:AM3"/>
@@ -9668,18 +9678,8 @@
     <mergeCell ref="P5:P13"/>
     <mergeCell ref="W5:W13"/>
     <mergeCell ref="AD5:AD13"/>
-    <mergeCell ref="I18:I25"/>
-    <mergeCell ref="P18:P25"/>
-    <mergeCell ref="W18:W25"/>
-    <mergeCell ref="AD18:AD25"/>
-    <mergeCell ref="A15:AM15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="AH16:AM16"/>
     <mergeCell ref="D5:D13"/>
     <mergeCell ref="G5:G13"/>
-    <mergeCell ref="D18:D25"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="G18:G25"/>
   </mergeCells>
   <conditionalFormatting sqref="D18:E25">
     <cfRule type="cellIs" dxfId="116" priority="5" operator="equal">
@@ -9687,11 +9687,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:F25">
-    <cfRule type="cellIs" dxfId="115" priority="7" operator="equal">
+    <cfRule type="expression" dxfId="115" priority="6">
+      <formula>D$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="7" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="114" priority="6">
-      <formula>D$3="SUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="113" priority="8" operator="equal">
       <formula>"P"</formula>
@@ -9703,39 +9703,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:AG13 AM13">
-    <cfRule type="cellIs" dxfId="111" priority="114" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="81" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="114" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="113" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="113" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="81" operator="equal">
-      <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F25 H18:K25">
-    <cfRule type="cellIs" dxfId="108" priority="96" operator="equal">
+    <cfRule type="expression" dxfId="108" priority="94">
+      <formula>F$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="107" priority="96" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="95" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="106" priority="94">
-      <formula>F$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18:G25">
-    <cfRule type="expression" dxfId="105" priority="2">
+    <cfRule type="cellIs" dxfId="105" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="2">
       <formula>G$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="3" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="4" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="1" operator="equal">
-      <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:AG25 F18:F25">
@@ -9744,25 +9744,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18">
-    <cfRule type="cellIs" dxfId="100" priority="68" operator="equal">
+    <cfRule type="expression" dxfId="100" priority="67">
+      <formula>I$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="68" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="67">
-      <formula>I$3="SUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="98" priority="69" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J18:L25">
-    <cfRule type="expression" dxfId="97" priority="43">
+    <cfRule type="cellIs" dxfId="97" priority="45" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="43">
       <formula>J$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="44" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="45" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
@@ -9777,66 +9777,66 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:R25">
-    <cfRule type="cellIs" dxfId="91" priority="93" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="91" priority="91">
+      <formula>M$3="SUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="90" priority="92" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="91">
-      <formula>M$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="89" priority="93" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18">
-    <cfRule type="cellIs" dxfId="88" priority="66" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="88" priority="64">
+      <formula>P$3="SUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="87" priority="65" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="64">
-      <formula>P$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="86" priority="66" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18">
-    <cfRule type="expression" dxfId="85" priority="100">
+    <cfRule type="cellIs" dxfId="85" priority="102" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="101" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="100">
       <formula>S$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="102" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="101" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:S25">
-    <cfRule type="expression" dxfId="82" priority="40">
-      <formula>S$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="82" priority="41" operator="equal">
+      <formula>"A"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="81" priority="42" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="41" operator="equal">
-      <formula>"A"</formula>
+    <cfRule type="expression" dxfId="80" priority="40">
+      <formula>S$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:Y25">
-    <cfRule type="cellIs" dxfId="79" priority="90" operator="equal">
+    <cfRule type="expression" dxfId="79" priority="88">
+      <formula>T$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="89" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="77" priority="90" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="88">
-      <formula>T$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="89" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W18">
-    <cfRule type="cellIs" dxfId="76" priority="62" operator="equal">
+    <cfRule type="expression" dxfId="76" priority="61">
+      <formula>W$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="62" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="61">
-      <formula>W$3="SUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="74" priority="63" operator="equal">
       <formula>"P"</formula>
@@ -9868,11 +9868,11 @@
     <cfRule type="expression" dxfId="67" priority="85">
       <formula>AA$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="86" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="87" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="86" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD18">
@@ -9887,25 +9887,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE18">
-    <cfRule type="cellIs" dxfId="61" priority="80" operator="equal">
+    <cfRule type="expression" dxfId="61" priority="78">
+      <formula>AE$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="79" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="59" priority="80" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="78">
-      <formula>AE$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="79" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE18:AF25">
-    <cfRule type="cellIs" dxfId="58" priority="27" operator="equal">
+    <cfRule type="expression" dxfId="58" priority="25">
+      <formula>AE$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="27" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="26" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="25">
-      <formula>AE$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18:AG25">
@@ -9940,40 +9940,40 @@
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="36"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="41"/>
     </row>
     <row r="3" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="67"/>
+      <c r="A3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
       <c r="D3" s="30" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Thu</v>
@@ -10038,14 +10038,14 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="T3" s="39" t="s">
+      <c r="T3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="41"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="47"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10134,7 +10134,7 @@
       <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="69" t="s">
         <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -10143,7 +10143,7 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -10164,7 +10164,7 @@
       <c r="M5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="42" t="s">
+      <c r="N5" s="48" t="s">
         <v>26</v>
       </c>
       <c r="O5" s="4" t="s">
@@ -10215,14 +10215,14 @@
       <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="63"/>
+      <c r="D6" s="69"/>
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="42"/>
+      <c r="G6" s="48"/>
       <c r="H6" s="4" t="s">
         <v>6</v>
       </c>
@@ -10241,7 +10241,7 @@
       <c r="M6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="42"/>
+      <c r="N6" s="48"/>
       <c r="O6" s="4" t="s">
         <v>6</v>
       </c>
@@ -10290,14 +10290,14 @@
       <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="63"/>
+      <c r="D7" s="69"/>
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="42"/>
+      <c r="G7" s="48"/>
       <c r="H7" s="4" t="s">
         <v>6</v>
       </c>
@@ -10316,7 +10316,7 @@
       <c r="M7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="42"/>
+      <c r="N7" s="48"/>
       <c r="O7" s="4" t="s">
         <v>6</v>
       </c>
@@ -10365,14 +10365,14 @@
       <c r="C8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="63"/>
+      <c r="D8" s="69"/>
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="42"/>
+      <c r="G8" s="48"/>
       <c r="H8" s="4" t="s">
         <v>6</v>
       </c>
@@ -10391,7 +10391,7 @@
       <c r="M8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N8" s="42"/>
+      <c r="N8" s="48"/>
       <c r="O8" s="4" t="s">
         <v>6</v>
       </c>
@@ -10440,14 +10440,14 @@
       <c r="C9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="63"/>
+      <c r="D9" s="69"/>
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="42"/>
+      <c r="G9" s="48"/>
       <c r="H9" s="4" t="s">
         <v>6</v>
       </c>
@@ -10466,7 +10466,7 @@
       <c r="M9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N9" s="42"/>
+      <c r="N9" s="48"/>
       <c r="O9" s="4" t="s">
         <v>6</v>
       </c>
@@ -10515,14 +10515,14 @@
       <c r="C10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="63"/>
+      <c r="D10" s="69"/>
       <c r="E10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="48"/>
       <c r="H10" s="4" t="s">
         <v>6</v>
       </c>
@@ -10541,7 +10541,7 @@
       <c r="M10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="42"/>
+      <c r="N10" s="48"/>
       <c r="O10" s="4" t="s">
         <v>6</v>
       </c>
@@ -10590,14 +10590,14 @@
       <c r="C11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="63"/>
+      <c r="D11" s="69"/>
       <c r="E11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="42"/>
+      <c r="G11" s="48"/>
       <c r="H11" s="4" t="s">
         <v>6</v>
       </c>
@@ -10616,7 +10616,7 @@
       <c r="M11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N11" s="42"/>
+      <c r="N11" s="48"/>
       <c r="O11" s="4" t="s">
         <v>6</v>
       </c>
@@ -10665,14 +10665,14 @@
       <c r="C12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="64"/>
+      <c r="D12" s="70"/>
       <c r="E12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="43"/>
+      <c r="G12" s="49"/>
       <c r="H12" s="4" t="s">
         <v>6</v>
       </c>
@@ -10691,7 +10691,7 @@
       <c r="M12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N12" s="43"/>
+      <c r="N12" s="49"/>
       <c r="O12" s="4" t="s">
         <v>6</v>
       </c>
@@ -10740,14 +10740,14 @@
       <c r="C13" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="64"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="43"/>
+      <c r="G13" s="49"/>
       <c r="H13" s="4" t="s">
         <v>6</v>
       </c>
@@ -10766,7 +10766,7 @@
       <c r="M13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="43"/>
+      <c r="N13" s="49"/>
       <c r="O13" s="4" t="s">
         <v>6</v>
       </c>
@@ -10815,14 +10815,14 @@
       <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="65"/>
+      <c r="D14" s="71"/>
       <c r="E14" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="44"/>
+      <c r="G14" s="50"/>
       <c r="H14" s="6" t="s">
         <v>6</v>
       </c>
@@ -10841,7 +10841,7 @@
       <c r="M14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="N14" s="44"/>
+      <c r="N14" s="50"/>
       <c r="O14" s="6" t="s">
         <v>6</v>
       </c>
@@ -10882,40 +10882,40 @@
     </row>
     <row r="15" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="36"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="40"/>
+      <c r="Y16" s="41"/>
     </row>
     <row r="17" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="66"/>
+      <c r="A17" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="72"/>
       <c r="D17" s="30" t="str">
         <f>TEXT(D18,"ddd")</f>
         <v>Thu</v>
@@ -10980,14 +10980,14 @@
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="T17" s="39" t="s">
+      <c r="T17" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="U17" s="40"/>
-      <c r="V17" s="40"/>
-      <c r="W17" s="40"/>
-      <c r="X17" s="40"/>
-      <c r="Y17" s="41"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="46"/>
+      <c r="Y17" s="47"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -11077,7 +11077,7 @@
       <c r="C19" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="63" t="s">
+      <c r="D19" s="69" t="s">
         <v>46</v>
       </c>
       <c r="E19" s="4" t="s">
@@ -11086,7 +11086,7 @@
       <c r="F19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="43" t="s">
+      <c r="G19" s="49" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -11107,7 +11107,7 @@
       <c r="M19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N19" s="43" t="s">
+      <c r="N19" s="49" t="s">
         <v>26</v>
       </c>
       <c r="O19" s="4" t="s">
@@ -11159,14 +11159,14 @@
       <c r="C20" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="63"/>
+      <c r="D20" s="69"/>
       <c r="E20" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="45"/>
+      <c r="G20" s="51"/>
       <c r="H20" s="4" t="s">
         <v>6</v>
       </c>
@@ -11185,7 +11185,7 @@
       <c r="M20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="45"/>
+      <c r="N20" s="51"/>
       <c r="O20" s="4" t="s">
         <v>6</v>
       </c>
@@ -11235,14 +11235,14 @@
       <c r="C21" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="63"/>
+      <c r="D21" s="69"/>
       <c r="E21" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="45"/>
+      <c r="G21" s="51"/>
       <c r="H21" s="4" t="s">
         <v>6</v>
       </c>
@@ -11261,7 +11261,7 @@
       <c r="M21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="45"/>
+      <c r="N21" s="51"/>
       <c r="O21" s="4" t="s">
         <v>6</v>
       </c>
@@ -11311,14 +11311,14 @@
       <c r="C22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="63"/>
+      <c r="D22" s="69"/>
       <c r="E22" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="45"/>
+      <c r="G22" s="51"/>
       <c r="H22" s="4" t="s">
         <v>6</v>
       </c>
@@ -11337,7 +11337,7 @@
       <c r="M22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N22" s="45"/>
+      <c r="N22" s="51"/>
       <c r="O22" s="4" t="s">
         <v>6</v>
       </c>
@@ -11387,14 +11387,14 @@
       <c r="C23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="63"/>
+      <c r="D23" s="69"/>
       <c r="E23" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="45"/>
+      <c r="G23" s="51"/>
       <c r="H23" s="4" t="s">
         <v>6</v>
       </c>
@@ -11413,7 +11413,7 @@
       <c r="M23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N23" s="45"/>
+      <c r="N23" s="51"/>
       <c r="O23" s="4" t="s">
         <v>6</v>
       </c>
@@ -11463,14 +11463,14 @@
       <c r="C24" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="63"/>
+      <c r="D24" s="69"/>
       <c r="E24" s="4" t="s">
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="45"/>
+      <c r="G24" s="51"/>
       <c r="H24" s="4" t="s">
         <v>6</v>
       </c>
@@ -11489,7 +11489,7 @@
       <c r="M24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N24" s="45"/>
+      <c r="N24" s="51"/>
       <c r="O24" s="4" t="s">
         <v>6</v>
       </c>
@@ -11539,14 +11539,14 @@
       <c r="C25" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="63"/>
+      <c r="D25" s="69"/>
       <c r="E25" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="45"/>
+      <c r="G25" s="51"/>
       <c r="H25" s="11" t="s">
         <v>6</v>
       </c>
@@ -11565,7 +11565,7 @@
       <c r="M25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N25" s="45"/>
+      <c r="N25" s="51"/>
       <c r="O25" s="11" t="s">
         <v>6</v>
       </c>
@@ -11615,14 +11615,14 @@
       <c r="C26" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="65"/>
+      <c r="D26" s="71"/>
       <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="46"/>
+      <c r="G26" s="52"/>
       <c r="H26" s="6" t="s">
         <v>6</v>
       </c>
@@ -11641,7 +11641,7 @@
       <c r="M26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="N26" s="46"/>
+      <c r="N26" s="52"/>
       <c r="O26" s="6" t="s">
         <v>6</v>
       </c>
@@ -11682,11 +11682,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="T3:Y3"/>
-    <mergeCell ref="G5:G14"/>
-    <mergeCell ref="N5:N14"/>
     <mergeCell ref="G19:G26"/>
     <mergeCell ref="N19:N26"/>
     <mergeCell ref="D5:D14"/>
@@ -11694,6 +11689,11 @@
     <mergeCell ref="A16:Y16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="T17:Y17"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="T3:Y3"/>
+    <mergeCell ref="G5:G14"/>
+    <mergeCell ref="N5:N14"/>
   </mergeCells>
   <conditionalFormatting sqref="D19:D26">
     <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
@@ -11733,14 +11733,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="cellIs" dxfId="43" priority="104" operator="equal">
+    <cfRule type="expression" dxfId="43" priority="102">
+      <formula>E$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="104" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="103" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="103" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="102">
-      <formula>E$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:S26">
@@ -11752,33 +11752,33 @@
     <cfRule type="cellIs" dxfId="39" priority="92" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="91" operator="equal">
+    <cfRule type="expression" dxfId="38" priority="90">
+      <formula>F$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="91" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="90">
-      <formula>F$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19">
     <cfRule type="expression" dxfId="36" priority="21">
       <formula>G$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="23" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="22" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="23" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19">
-    <cfRule type="cellIs" dxfId="33" priority="68" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="33" priority="66">
+      <formula>I$3="SUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="32" priority="67" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="66">
-      <formula>I$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="31" priority="68" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:L26">
@@ -11793,69 +11793,69 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="27" priority="101" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="27" priority="99">
+      <formula>L$3="SUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="26" priority="100" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="99">
-      <formula>L$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="25" priority="101" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:R26">
     <cfRule type="cellIs" dxfId="24" priority="88" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="89" operator="equal">
+    <cfRule type="expression" dxfId="23" priority="87">
+      <formula>M$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="89" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="87">
-      <formula>M$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19">
-    <cfRule type="cellIs" dxfId="21" priority="16" operator="equal">
+    <cfRule type="expression" dxfId="21" priority="15">
+      <formula>N$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="15">
-      <formula>N$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:N26">
-    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="expression" dxfId="18" priority="18">
+      <formula>N$3="SUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="18">
-      <formula>N$3="SUN"</formula>
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P19">
     <cfRule type="cellIs" dxfId="15" priority="64" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="63">
+    <cfRule type="cellIs" dxfId="14" priority="65" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="63">
       <formula>P$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="65" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P19:P26">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+    <cfRule type="expression" dxfId="12" priority="9">
+      <formula>P$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="9">
-      <formula>P$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19">
@@ -11870,28 +11870,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:S26">
-    <cfRule type="cellIs" dxfId="6" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="40" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="39">
+      <formula>S$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="41" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="40" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="39">
-      <formula>S$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y5:Y14">
     <cfRule type="cellIs" dxfId="3" priority="69" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="70">
+    <cfRule type="cellIs" dxfId="2" priority="72" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="70">
       <formula>Y$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="71" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="72" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
